--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_4_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_4_branch.xlsx
@@ -646,10 +646,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.8010071194438338</v>
+        <v>0.8010071194438342</v>
       </c>
       <c r="C2">
-        <v>0.8010071194438338</v>
+        <v>0.8010071194438342</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27.74770056202225</v>
+        <v>27.74770056202226</v>
       </c>
       <c r="G2">
-        <v>27.74770056202225</v>
+        <v>27.74770056202226</v>
       </c>
       <c r="H2">
-        <v>3.346522574404278</v>
+        <v>3.346522574404258</v>
       </c>
       <c r="I2">
-        <v>-2.345607201329461</v>
+        <v>-2.34560720132944</v>
       </c>
       <c r="J2">
         <v>24.47415207745156</v>
@@ -676,22 +676,22 @@
         <v>-23.33849811301025</v>
       </c>
       <c r="L2">
-        <v>-82.99362927492926</v>
+        <v>-82.99362927492932</v>
       </c>
       <c r="M2">
-        <v>97.00637072506345</v>
+        <v>97.00637072506339</v>
       </c>
       <c r="N2">
-        <v>0.8902319386646703</v>
+        <v>0.8902319386646702</v>
       </c>
       <c r="O2">
-        <v>0.8453339436572478</v>
+        <v>0.8453339436572476</v>
       </c>
       <c r="P2">
-        <v>-0.7797968923376516</v>
+        <v>-0.779796892337649</v>
       </c>
       <c r="Q2">
-        <v>1.267200525268436</v>
+        <v>1.267200525268441</v>
       </c>
     </row>
   </sheetData>
@@ -843,127 +843,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6998997052421878</v>
+        <v>0.6998997052422463</v>
       </c>
       <c r="D2">
-        <v>0.6998997052421881</v>
+        <v>0.6998997052422454</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.6998997052421877</v>
+        <v>0.6998997052422462</v>
       </c>
       <c r="G2">
-        <v>0.6998997052421878</v>
+        <v>0.6998997052422454</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>8.081745664546338</v>
+        <v>8.081745664547013</v>
       </c>
       <c r="J2">
-        <v>8.081745664546341</v>
+        <v>8.081745664547002</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>8.081745664546336</v>
+        <v>8.081745664547013</v>
       </c>
       <c r="M2">
-        <v>8.081745664546338</v>
+        <v>8.081745664547002</v>
       </c>
       <c r="N2">
-        <v>-3.90798513137885E-15</v>
+        <v>3.907985131378814E-15</v>
       </c>
       <c r="O2">
-        <v>5.292305046837879</v>
+        <v>5.292305046837614</v>
       </c>
       <c r="P2">
-        <v>-3.53211323517333</v>
+        <v>-3.532113235174423</v>
       </c>
       <c r="Q2">
-        <v>2.605323420919224E-15</v>
+        <v>-5.210646841838418E-15</v>
       </c>
       <c r="R2">
-        <v>-5.037578050935243</v>
+        <v>-5.037578050934933</v>
       </c>
       <c r="S2">
-        <v>3.786840231075973</v>
+        <v>3.786840231077104</v>
       </c>
       <c r="T2">
-        <v>2.605323420919295E-15</v>
+        <v>-6.513308552297955E-16</v>
       </c>
       <c r="U2">
-        <v>5.972767149283233</v>
+        <v>5.972767149283757</v>
       </c>
       <c r="V2">
-        <v>7.049951963208347</v>
+        <v>7.049951963208223</v>
       </c>
       <c r="W2">
-        <v>-2.605323420919281E-15</v>
+        <v>6.51330855229793E-16</v>
       </c>
       <c r="X2">
-        <v>-5.683749985066477</v>
+        <v>-5.683749985066951</v>
       </c>
       <c r="Y2">
-        <v>-6.760934798991589</v>
+        <v>-6.760934798991422</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-173.040413033096</v>
+        <v>-173.0404130331013</v>
       </c>
       <c r="AB2">
-        <v>6.959586966896772</v>
+        <v>6.959586966891396</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>6.959586966896747</v>
+        <v>6.959586966891442</v>
       </c>
       <c r="AE2">
-        <v>-173.0404130330959</v>
+        <v>-173.0404130331013</v>
       </c>
       <c r="AF2">
-        <v>1.10000002384046</v>
+        <v>1.100000023840441</v>
       </c>
       <c r="AG2">
-        <v>0.9874262514316039</v>
+        <v>0.9874262514315478</v>
       </c>
       <c r="AH2">
-        <v>0.9756902409610327</v>
+        <v>0.9756902409609998</v>
       </c>
       <c r="AI2">
-        <v>1.10000002384046</v>
+        <v>1.100000023840441</v>
       </c>
       <c r="AJ2">
-        <v>0.9397573987320329</v>
+        <v>0.9397573987319728</v>
       </c>
       <c r="AK2">
-        <v>0.958854624602045</v>
+        <v>0.9588546246020166</v>
       </c>
       <c r="AL2">
-        <v>-6.218649317347489E-13</v>
+        <v>9.835047058114384E-14</v>
       </c>
       <c r="AM2">
-        <v>-124.5836849065161</v>
+        <v>-124.5836849065175</v>
       </c>
       <c r="AN2">
-        <v>123.5710235817494</v>
+        <v>123.5710235817515</v>
       </c>
       <c r="AO2">
-        <v>-6.218068357145651E-13</v>
+        <v>1.000681686955674E-13</v>
       </c>
       <c r="AP2">
-        <v>-124.591381898106</v>
+        <v>-124.5913818981072</v>
       </c>
       <c r="AQ2">
-        <v>126.2130370813425</v>
+        <v>126.2130370813451</v>
       </c>
     </row>
   </sheetData>
@@ -1115,91 +1115,91 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.001186337663406363</v>
+        <v>0.001186337663406362</v>
       </c>
       <c r="D2">
-        <v>0.001186337663406366</v>
+        <v>0.001186337663406367</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.001186337663406364</v>
+        <v>0.001186337663406362</v>
       </c>
       <c r="G2">
-        <v>0.001186337663406365</v>
+        <v>0.001186337663406367</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01369864738634911</v>
+        <v>0.0136986473863491</v>
       </c>
       <c r="J2">
-        <v>0.01369864738634914</v>
+        <v>0.01369864738634916</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01369864738634912</v>
+        <v>0.01369864738634909</v>
       </c>
       <c r="M2">
-        <v>0.01369864738634913</v>
+        <v>0.01369864738634915</v>
       </c>
       <c r="N2">
-        <v>1.214306378038389E-17</v>
+        <v>6.557254441407298E-17</v>
       </c>
       <c r="O2">
         <v>0.01388939212212888</v>
       </c>
       <c r="P2">
-        <v>0.003707964292099923</v>
+        <v>0.003707964292099924</v>
       </c>
       <c r="Q2">
-        <v>-2.428612756076777E-18</v>
+        <v>-6.800115717014975E-17</v>
       </c>
       <c r="R2">
-        <v>-0.01388866027564695</v>
+        <v>-0.01388866027564693</v>
       </c>
       <c r="S2">
-        <v>-0.003707232445617984</v>
+        <v>-0.003707232445617982</v>
       </c>
       <c r="T2">
-        <v>-4.934478921784046E-34</v>
+        <v>1.19410361289398E-34</v>
       </c>
       <c r="U2">
-        <v>0.003734119487648208</v>
+        <v>0.003734119487648176</v>
       </c>
       <c r="V2">
-        <v>0.01389413302793225</v>
+        <v>0.01389413302793227</v>
       </c>
       <c r="W2">
-        <v>2.428612756076777E-18</v>
+        <v>-8.168080123105755E-35</v>
       </c>
       <c r="X2">
-        <v>-0.003733289123382728</v>
+        <v>-0.003733289123382688</v>
       </c>
       <c r="Y2">
-        <v>-0.01389330266366675</v>
+        <v>-0.01389330266366678</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-135.0603176514361</v>
+        <v>-135.060317651436</v>
       </c>
       <c r="AB2">
-        <v>44.93968234855657</v>
+        <v>44.93968234855654</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.93968234855657</v>
+        <v>44.93968234855669</v>
       </c>
       <c r="AE2">
-        <v>-135.0603176514361</v>
+        <v>-135.0603176514362</v>
       </c>
       <c r="AF2">
         <v>1.049999952316282</v>
@@ -1214,13 +1214,13 @@
         <v>1.049999952316282</v>
       </c>
       <c r="AJ2">
-        <v>1.049860334070205</v>
+        <v>1.049860334070204</v>
       </c>
       <c r="AK2">
         <v>1.049695606600145</v>
       </c>
       <c r="AL2">
-        <v>-2.328282395841468E-15</v>
+        <v>1.043380242927744E-16</v>
       </c>
       <c r="AM2">
         <v>-120.0123410858218</v>
@@ -1229,7 +1229,7 @@
         <v>119.9972465564479</v>
       </c>
       <c r="AO2">
-        <v>-2.331561961334362E-15</v>
+        <v>6.88218461647111E-17</v>
       </c>
       <c r="AP2">
         <v>-120.0147787920383</v>
@@ -1387,28 +1387,28 @@
         <v>0</v>
       </c>
       <c r="C2">
+        <v>0.001242766873429835</v>
+      </c>
+      <c r="D2">
+        <v>0.001242766873429835</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>0.001242766873429834</v>
       </c>
-      <c r="D2">
-        <v>0.001242766873429833</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0.001242766873429833</v>
-      </c>
       <c r="G2">
-        <v>0.001242766873429833</v>
+        <v>0.001242766873429836</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01435023577829328</v>
+        <v>0.01435023577829329</v>
       </c>
       <c r="J2">
-        <v>0.01435023577829328</v>
+        <v>0.0143502357782933</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1417,61 +1417,61 @@
         <v>0.01435023577829328</v>
       </c>
       <c r="M2">
-        <v>0.01435023577829327</v>
+        <v>0.0143502357782933</v>
       </c>
       <c r="N2">
-        <v>3.816391729867029E-18</v>
+        <v>5.644174453174073E-36</v>
       </c>
       <c r="O2">
-        <v>0.01524274420999386</v>
+        <v>0.01524274420999387</v>
       </c>
       <c r="P2">
-        <v>0.004068673653205679</v>
+        <v>0.004068673653205708</v>
       </c>
       <c r="Q2">
-        <v>-6.360652883111716E-18</v>
+        <v>-1.272130576622343E-18</v>
       </c>
       <c r="R2">
-        <v>-0.0152419410858364</v>
+        <v>-0.01524194108583642</v>
       </c>
       <c r="S2">
-        <v>-0.004067870529048221</v>
+        <v>-0.004067870529048255</v>
       </c>
       <c r="T2">
-        <v>7.632783459734058E-18</v>
+        <v>-2.544261153244686E-18</v>
       </c>
       <c r="U2">
-        <v>0.004098641437294996</v>
+        <v>0.004098641437294981</v>
       </c>
       <c r="V2">
-        <v>0.01524828586810063</v>
+        <v>0.01524828586810064</v>
       </c>
       <c r="W2">
-        <v>-2.544261153244686E-18</v>
+        <v>-2.836647397209867E-36</v>
       </c>
       <c r="X2">
-        <v>-0.004097730200283471</v>
+        <v>-0.004097730200283455</v>
       </c>
       <c r="Y2">
-        <v>-0.0152473746310891</v>
+        <v>-0.01524737463108912</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-135.0626917773677</v>
+        <v>-135.0626917773676</v>
       </c>
       <c r="AB2">
-        <v>44.93730822262505</v>
+        <v>44.93730822262513</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.93730822262506</v>
+        <v>44.93730822262513</v>
       </c>
       <c r="AE2">
-        <v>-135.0626917773677</v>
+        <v>-135.0626917773676</v>
       </c>
       <c r="AF2">
         <v>1.100000023841856</v>
@@ -1492,7 +1492,7 @@
         <v>1.099681201022603</v>
       </c>
       <c r="AL2">
-        <v>-6.601332215138165E-16</v>
+        <v>1.271046309809848E-16</v>
       </c>
       <c r="AM2">
         <v>-120.0123402953707</v>
@@ -1501,7 +1501,7 @@
         <v>119.9972472210367</v>
       </c>
       <c r="AO2">
-        <v>-6.555949984537322E-16</v>
+        <v>1.277604098302705E-16</v>
       </c>
       <c r="AP2">
         <v>-120.0147777254427</v>
@@ -1659,127 +1659,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5966140229780447</v>
+        <v>0.5966140229781119</v>
       </c>
       <c r="D2">
-        <v>0.5966140229780449</v>
+        <v>0.5966140229781126</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.5966140229780447</v>
+        <v>0.5966140229781119</v>
       </c>
       <c r="G2">
-        <v>0.5966140229780451</v>
+        <v>0.5966140229781126</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>6.889105335373594</v>
+        <v>6.889105335374371</v>
       </c>
       <c r="J2">
-        <v>6.889105335373596</v>
+        <v>6.889105335374378</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6.889105335373594</v>
+        <v>6.889105335374371</v>
       </c>
       <c r="M2">
-        <v>6.889105335373598</v>
+        <v>6.889105335374378</v>
       </c>
       <c r="N2">
-        <v>-1.125025984170068E-15</v>
+        <v>-5.625129920849527E-15</v>
       </c>
       <c r="O2">
-        <v>4.046129872853161</v>
+        <v>4.046129872853331</v>
       </c>
       <c r="P2">
-        <v>-2.424144743558061</v>
+        <v>-2.424144743558886</v>
       </c>
       <c r="Q2">
-        <v>1.125025984170142E-15</v>
+        <v>5.625129920849527E-15</v>
       </c>
       <c r="R2">
-        <v>-3.690751090374668</v>
+        <v>-3.690751090374756</v>
       </c>
       <c r="S2">
-        <v>2.779523526036563</v>
+        <v>2.779523526037468</v>
       </c>
       <c r="T2">
-        <v>2.812564960424635E-15</v>
+        <v>2.250051968339797E-15</v>
       </c>
       <c r="U2">
-        <v>4.251377237039582</v>
+        <v>4.25137723704005</v>
       </c>
       <c r="V2">
-        <v>5.235241980681035</v>
+        <v>5.235241980681923</v>
       </c>
       <c r="W2">
-        <v>-3.937590944594519E-15</v>
+        <v>-2.250051968339797E-15</v>
       </c>
       <c r="X2">
-        <v>-4.041367743242323</v>
+        <v>-4.041367743242744</v>
       </c>
       <c r="Y2">
-        <v>-5.025232486883782</v>
+        <v>-5.025232486884621</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-171.3538824675767</v>
+        <v>-171.3538824675771</v>
       </c>
       <c r="AB2">
-        <v>8.646117532415992</v>
+        <v>8.646117532415621</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>8.646117532415973</v>
+        <v>8.646117532415639</v>
       </c>
       <c r="AE2">
-        <v>-171.3538824675767</v>
+        <v>-171.3538824675771</v>
       </c>
       <c r="AF2">
-        <v>0.9499999880793025</v>
+        <v>0.9499999880793201</v>
       </c>
       <c r="AG2">
-        <v>0.8519274965731399</v>
+        <v>0.8519274965731101</v>
       </c>
       <c r="AH2">
-        <v>0.8374453458530067</v>
+        <v>0.8374453458530791</v>
       </c>
       <c r="AI2">
-        <v>0.9499999880793024</v>
+        <v>0.9499999880793201</v>
       </c>
       <c r="AJ2">
-        <v>0.7944503111014809</v>
+        <v>0.7944503111014452</v>
       </c>
       <c r="AK2">
-        <v>0.8335929320137906</v>
+        <v>0.8335929320138664</v>
       </c>
       <c r="AL2">
-        <v>3.755740198093717E-12</v>
+        <v>1.17273175458324E-13</v>
       </c>
       <c r="AM2">
-        <v>-124.9369014450644</v>
+        <v>-124.9369014450627</v>
       </c>
       <c r="AN2">
-        <v>123.4923062495796</v>
+        <v>123.492306249583</v>
       </c>
       <c r="AO2">
-        <v>3.760677192641919E-12</v>
+        <v>1.209192263254526E-13</v>
       </c>
       <c r="AP2">
-        <v>-123.7575563059346</v>
+        <v>-123.7575563059327</v>
       </c>
       <c r="AQ2">
-        <v>127.5936876756924</v>
+        <v>127.5936876756959</v>
       </c>
     </row>
   </sheetData>
@@ -1931,127 +1931,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5652132770460215</v>
+        <v>0.5652132770460854</v>
       </c>
       <c r="D2">
-        <v>0.5652132770460223</v>
+        <v>0.5652132770460856</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.5652132770460218</v>
+        <v>0.5652132770460854</v>
       </c>
       <c r="G2">
-        <v>0.5652132770460221</v>
+        <v>0.5652132770460857</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>6.526520753041422</v>
+        <v>6.526520753042159</v>
       </c>
       <c r="J2">
-        <v>6.526520753041431</v>
+        <v>6.526520753042162</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6.526520753041424</v>
+        <v>6.526520753042159</v>
       </c>
       <c r="M2">
-        <v>6.526520753041428</v>
+        <v>6.526520753042163</v>
       </c>
       <c r="N2">
-        <v>5.329070377030992E-16</v>
+        <v>-5.329070377029993E-15</v>
       </c>
       <c r="O2">
-        <v>3.631429479912414</v>
+        <v>3.631429479912645</v>
       </c>
       <c r="P2">
-        <v>-2.175686634380235</v>
+        <v>-2.175686634380591</v>
       </c>
       <c r="Q2">
-        <v>1.065814075405951E-15</v>
+        <v>4.263256301623994E-15</v>
       </c>
       <c r="R2">
-        <v>-3.312474570460195</v>
+        <v>-3.312474570460352</v>
       </c>
       <c r="S2">
-        <v>2.494641543832464</v>
+        <v>2.494641543832892</v>
       </c>
       <c r="T2">
-        <v>2.131628150812047E-15</v>
+        <v>1.598721113108986E-15</v>
       </c>
       <c r="U2">
-        <v>3.815640405513873</v>
+        <v>3.81564040551411</v>
       </c>
       <c r="V2">
-        <v>4.698665801776289</v>
+        <v>4.698665801777086</v>
       </c>
       <c r="W2">
-        <v>-2.131628150812108E-15</v>
+        <v>-1.065814075405989E-15</v>
       </c>
       <c r="X2">
-        <v>-3.627155435727403</v>
+        <v>-3.627155435727596</v>
       </c>
       <c r="Y2">
-        <v>-4.510180831989818</v>
+        <v>-4.510180831990575</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-171.3538824675767</v>
+        <v>-171.3538824675771</v>
       </c>
       <c r="AB2">
-        <v>8.646117532416024</v>
+        <v>8.646117532415605</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>8.646117532415996</v>
+        <v>8.6461175324156</v>
       </c>
       <c r="AE2">
-        <v>-171.3538824675767</v>
+        <v>-171.3538824675771</v>
       </c>
       <c r="AF2">
-        <v>0.8999999761584081</v>
+        <v>0.899999976158378</v>
       </c>
       <c r="AG2">
-        <v>0.807089196026901</v>
+        <v>0.8070891960268606</v>
       </c>
       <c r="AH2">
-        <v>0.7933692639570255</v>
+        <v>0.7933692639570702</v>
       </c>
       <c r="AI2">
-        <v>0.899999976158408</v>
+        <v>0.899999976158378</v>
       </c>
       <c r="AJ2">
-        <v>0.7526371263392707</v>
+        <v>0.7526371263392241</v>
       </c>
       <c r="AK2">
-        <v>0.7897196087918155</v>
+        <v>0.7897196087918598</v>
       </c>
       <c r="AL2">
-        <v>-2.212263027204939E-12</v>
+        <v>1.165448181665704E-13</v>
       </c>
       <c r="AM2">
-        <v>-124.9369014450623</v>
+        <v>-124.9369014450627</v>
       </c>
       <c r="AN2">
-        <v>123.4923062495835</v>
+        <v>123.492306249583</v>
       </c>
       <c r="AO2">
-        <v>-2.208251636219828E-12</v>
+        <v>1.194945119704732E-13</v>
       </c>
       <c r="AP2">
-        <v>-123.7575563059325</v>
+        <v>-123.7575563059327</v>
       </c>
       <c r="AQ2">
-        <v>127.5936876756962</v>
+        <v>127.5936876756959</v>
       </c>
     </row>
   </sheetData>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.001073244566638008</v>
+        <v>0.001073244566638007</v>
       </c>
       <c r="D2">
         <v>0.001073244566638009</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.001073244566638009</v>
+        <v>0.001073244566638007</v>
       </c>
       <c r="G2">
         <v>0.001073244566638009</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01239276078909515</v>
+        <v>0.01239276078909513</v>
       </c>
       <c r="J2">
         <v>0.01239276078909516</v>
@@ -2230,43 +2230,43 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01239276078909515</v>
+        <v>0.01239276078909513</v>
       </c>
       <c r="M2">
         <v>0.01239276078909516</v>
       </c>
       <c r="N2">
-        <v>-8.23993640749229E-19</v>
+        <v>-2.444514467556045E-17</v>
       </c>
       <c r="O2">
         <v>0.01136857461527819</v>
       </c>
       <c r="P2">
-        <v>0.003034847464254069</v>
+        <v>0.003034847464254067</v>
       </c>
       <c r="Q2">
-        <v>2.197316375331276E-18</v>
+        <v>2.389581558172763E-17</v>
       </c>
       <c r="R2">
-        <v>-0.01136742460432089</v>
+        <v>-0.01136742460432088</v>
       </c>
       <c r="S2">
-        <v>-0.003033697453296762</v>
+        <v>-0.00303369745329676</v>
       </c>
       <c r="T2">
-        <v>-2.197316375331277E-18</v>
+        <v>-1.098658187665638E-18</v>
       </c>
       <c r="U2">
-        <v>0.003056449564971675</v>
+        <v>0.00305644956497165</v>
       </c>
       <c r="V2">
         <v>0.01137242260315678</v>
       </c>
       <c r="W2">
-        <v>-4.394632750662553E-18</v>
+        <v>1.098658187665638E-18</v>
       </c>
       <c r="X2">
-        <v>-0.00305576997116666</v>
+        <v>-0.003055769971166638</v>
       </c>
       <c r="Y2">
         <v>-0.01137174300935177</v>
@@ -2275,49 +2275,49 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-135.0610963162982</v>
+        <v>-135.0610963162981</v>
       </c>
       <c r="AB2">
-        <v>44.93890368369452</v>
+        <v>44.9389036836945</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.93890368369449</v>
+        <v>44.93890368369458</v>
       </c>
       <c r="AE2">
         <v>-135.0610963162982</v>
       </c>
       <c r="AF2">
-        <v>0.9499999880790746</v>
+        <v>0.9499999880790745</v>
       </c>
       <c r="AG2">
-        <v>0.9499312985903278</v>
+        <v>0.9499312985903279</v>
       </c>
       <c r="AH2">
-        <v>0.9497802226059047</v>
+        <v>0.9497802226059048</v>
       </c>
       <c r="AI2">
-        <v>0.9499999880790746</v>
+        <v>0.9499999880790745</v>
       </c>
       <c r="AJ2">
-        <v>0.9498274465944991</v>
+        <v>0.9498274465944992</v>
       </c>
       <c r="AK2">
         <v>0.9497033152804071</v>
       </c>
       <c r="AL2">
-        <v>-4.778047207553018E-15</v>
+        <v>1.865258171185791E-16</v>
       </c>
       <c r="AM2">
-        <v>-120.0129131626925</v>
+        <v>-120.0129131626926</v>
       </c>
       <c r="AN2">
         <v>119.9971322138701</v>
       </c>
       <c r="AO2">
-        <v>-4.778228590830113E-15</v>
+        <v>1.886653865196761E-16</v>
       </c>
       <c r="AP2">
         <v>-120.0146543330407</v>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.001016757996322908</v>
+        <v>0.001016757996322907</v>
       </c>
       <c r="D2">
         <v>0.001016757996322909</v>
@@ -2484,103 +2484,103 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.001016757996322908</v>
+        <v>0.001016757996322907</v>
       </c>
       <c r="G2">
-        <v>0.001016757996322909</v>
+        <v>0.00101675799632291</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01174051005755471</v>
+        <v>0.0117405100575547</v>
       </c>
       <c r="J2">
-        <v>0.01174051005755472</v>
+        <v>0.01174051005755473</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01174051005755471</v>
+        <v>0.0117405100575547</v>
       </c>
       <c r="M2">
-        <v>0.01174051005755472</v>
+        <v>0.01174051005755473</v>
       </c>
       <c r="N2">
-        <v>7.806255435100506E-19</v>
+        <v>-2.367897481980487E-17</v>
       </c>
       <c r="O2">
-        <v>0.01020337416243</v>
+        <v>0.01020337416242999</v>
       </c>
       <c r="P2">
         <v>0.002723796540163571</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.263814076179147E-17</v>
       </c>
       <c r="R2">
-        <v>-0.01020234201966054</v>
+        <v>-0.01020234201966053</v>
       </c>
       <c r="S2">
-        <v>-0.002722764397394105</v>
+        <v>-0.002722764397394108</v>
       </c>
       <c r="T2">
+        <v>2.081668116026802E-18</v>
+      </c>
+      <c r="U2">
+        <v>0.002743184574616</v>
+      </c>
+      <c r="V2">
+        <v>0.01020682775810285</v>
+      </c>
+      <c r="W2">
         <v>-1.040834058013401E-18</v>
       </c>
-      <c r="U2">
-        <v>0.002743184574616016</v>
-      </c>
-      <c r="V2">
-        <v>0.01020682775810284</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
       <c r="X2">
-        <v>-0.002742574634486698</v>
+        <v>-0.002742574634486677</v>
       </c>
       <c r="Y2">
-        <v>-0.01020621781797352</v>
+        <v>-0.01020621781797353</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-135.0610963162982</v>
+        <v>-135.0610963162981</v>
       </c>
       <c r="AB2">
-        <v>44.93890368369451</v>
+        <v>44.93890368369449</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>44.9389036836945</v>
+        <v>44.93890368369459</v>
       </c>
       <c r="AE2">
         <v>-135.0610963162982</v>
       </c>
       <c r="AF2">
-        <v>0.8999999761581454</v>
+        <v>0.8999999761581453</v>
       </c>
       <c r="AG2">
         <v>0.8999349019065559</v>
       </c>
       <c r="AH2">
-        <v>0.8997917772917292</v>
+        <v>0.8997917772917293</v>
       </c>
       <c r="AI2">
-        <v>0.8999999761581454</v>
+        <v>0.8999999761581453</v>
       </c>
       <c r="AJ2">
-        <v>0.8998365158066164</v>
+        <v>0.8998365158066162</v>
       </c>
       <c r="AK2">
-        <v>0.899718917721221</v>
+        <v>0.8997189177212213</v>
       </c>
       <c r="AL2">
-        <v>3.374804319767536E-15</v>
+        <v>1.864768278765768E-16</v>
       </c>
       <c r="AM2">
         <v>-120.0129131626926</v>
@@ -2589,7 +2589,7 @@
         <v>119.9971322138701</v>
       </c>
       <c r="AO2">
-        <v>3.376002462074428E-15</v>
+        <v>1.910994064824609E-16</v>
       </c>
       <c r="AP2">
         <v>-120.0146543330407</v>
@@ -2747,16 +2747,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.8095110032930093</v>
+        <v>0.8095110033054318</v>
       </c>
       <c r="C2">
-        <v>0.0002550743750417305</v>
+        <v>0.0002550743749290168</v>
       </c>
       <c r="D2">
-        <v>0.0002550743750412741</v>
+        <v>0.0002550743749296978</v>
       </c>
       <c r="E2">
-        <v>0.8093719610342632</v>
+        <v>0.8093719610466839</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2765,16 +2765,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.347427913263658</v>
+        <v>9.347427913407103</v>
       </c>
       <c r="I2">
-        <v>0.002945345181874373</v>
+        <v>0.002945345180572868</v>
       </c>
       <c r="J2">
-        <v>0.002945345181869104</v>
+        <v>0.002945345180580732</v>
       </c>
       <c r="K2">
-        <v>9.345822391553343</v>
+        <v>9.345822391696764</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2783,52 +2783,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.830876098911722</v>
+        <v>1.830876098445125</v>
       </c>
       <c r="O2">
-        <v>0.00287167851775863</v>
+        <v>0.002871678516742005</v>
       </c>
       <c r="P2">
-        <v>-0.0008539343573556258</v>
+        <v>-0.0008539343575655798</v>
       </c>
       <c r="Q2">
-        <v>-0.7982843257475838</v>
+        <v>-0.7982843252480025</v>
       </c>
       <c r="R2">
-        <v>7.333000764827943E-10</v>
+        <v>7.333000529995339E-10</v>
       </c>
       <c r="S2">
-        <v>-7.614311124188801E-10</v>
+        <v>-7.61428403361388E-10</v>
       </c>
       <c r="T2">
-        <v>8.522927073035065</v>
+        <v>8.522927073296298</v>
       </c>
       <c r="U2">
-        <v>0.0009240759623462338</v>
+        <v>0.0009240759613858412</v>
       </c>
       <c r="V2">
-        <v>-0.002924633071712274</v>
+        <v>-0.002924633070169644</v>
       </c>
       <c r="W2">
-        <v>-7.94282896897424</v>
+        <v>-7.942828969217917</v>
       </c>
       <c r="X2">
-        <v>-3.481634756277815E-10</v>
+        <v>-3.481579924625034E-10</v>
       </c>
       <c r="Y2">
-        <v>-5.148243971500904E-10</v>
+        <v>-5.14812568591508E-10</v>
       </c>
       <c r="Z2">
-        <v>-78.97044946479807</v>
+        <v>-78.97044946929458</v>
       </c>
       <c r="AA2">
-        <v>-135.9310760261182</v>
+        <v>-135.931076013537</v>
       </c>
       <c r="AB2">
-        <v>-135.9310760260751</v>
+        <v>-135.9310760136771</v>
       </c>
       <c r="AC2">
-        <v>101.0446874999864</v>
+        <v>101.04468749548</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -2837,40 +2837,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9325946855232489</v>
+        <v>0.9325946855257772</v>
       </c>
       <c r="AH2">
-        <v>1.02422489409676</v>
+        <v>1.024224894120898</v>
       </c>
       <c r="AI2">
-        <v>1.034428668892441</v>
+        <v>1.034428668862148</v>
       </c>
       <c r="AJ2">
-        <v>0.8541616925018247</v>
+        <v>0.8541616925093137</v>
       </c>
       <c r="AK2">
-        <v>0.9815906884322131</v>
+        <v>0.9815906884492555</v>
       </c>
       <c r="AL2">
-        <v>1.111435445797622</v>
+        <v>1.111435445768366</v>
       </c>
       <c r="AM2">
-        <v>-1.094348992885906</v>
+        <v>-1.094348994023459</v>
       </c>
       <c r="AN2">
-        <v>-118.0934464574586</v>
+        <v>-118.0934464563266</v>
       </c>
       <c r="AO2">
-        <v>117.7921755967598</v>
+        <v>117.7921755972369</v>
       </c>
       <c r="AP2">
-        <v>5.305517177319983</v>
+        <v>5.305517176556215</v>
       </c>
       <c r="AQ2">
-        <v>-121.7597765745311</v>
+        <v>-121.7597765731354</v>
       </c>
       <c r="AR2">
-        <v>117.7015826028264</v>
+        <v>117.7015826029557</v>
       </c>
     </row>
   </sheetData>
@@ -3022,16 +3022,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.8165582547719304</v>
+        <v>0.8165582547837821</v>
       </c>
       <c r="C2">
-        <v>0.0002572949418521293</v>
+        <v>0.0002572949417379874</v>
       </c>
       <c r="D2">
-        <v>0.0002572949418517433</v>
+        <v>0.0002572949417379639</v>
       </c>
       <c r="E2">
-        <v>0.816418002071622</v>
+        <v>0.8164180020834716</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3040,16 +3040,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.428802564031702</v>
+        <v>9.428802564168551</v>
       </c>
       <c r="I2">
-        <v>0.002970986078789119</v>
+        <v>0.002970986077471122</v>
       </c>
       <c r="J2">
-        <v>0.002970986078784662</v>
+        <v>0.002970986077470851</v>
       </c>
       <c r="K2">
-        <v>9.427183065346149</v>
+        <v>9.427183065482975</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3058,52 +3058,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.901475713596781</v>
+        <v>1.901475713120121</v>
       </c>
       <c r="O2">
-        <v>0.003035512744653922</v>
+        <v>0.003035512743577738</v>
       </c>
       <c r="P2">
-        <v>-0.0008874383057871994</v>
+        <v>-0.0008874383060378026</v>
       </c>
       <c r="Q2">
-        <v>-0.8509221379857289</v>
+        <v>-0.8509221374771957</v>
       </c>
       <c r="R2">
-        <v>7.786135538856169E-10</v>
+        <v>7.786152451831687E-10</v>
       </c>
       <c r="S2">
-        <v>-8.003114941391024E-10</v>
+        <v>-8.003040604066919E-10</v>
       </c>
       <c r="T2">
-        <v>9.056887154221535</v>
+        <v>9.05688715448408</v>
       </c>
       <c r="U2">
-        <v>0.0009843879976955394</v>
+        <v>0.0009843879966588908</v>
       </c>
       <c r="V2">
-        <v>-0.003096247859928251</v>
+        <v>-0.003096247858280892</v>
       </c>
       <c r="W2">
-        <v>-8.466568602449087</v>
+        <v>-8.466568602694752</v>
       </c>
       <c r="X2">
-        <v>-3.650182312136849E-10</v>
+        <v>-3.650085160870759E-10</v>
       </c>
       <c r="Y2">
-        <v>-5.465817030981211E-10</v>
+        <v>-5.46584008225264E-10</v>
       </c>
       <c r="Z2">
-        <v>-79.16805553530124</v>
+        <v>-79.16805553963322</v>
       </c>
       <c r="AA2">
-        <v>-136.1286820966602</v>
+        <v>-136.1286820838355</v>
       </c>
       <c r="AB2">
-        <v>-136.1286820966013</v>
+        <v>-136.128682083775</v>
       </c>
       <c r="AC2">
-        <v>100.8470814294832</v>
+        <v>100.8470814251414</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3112,40 +3112,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9814968825725385</v>
+        <v>0.9814968825751568</v>
       </c>
       <c r="AH2">
-        <v>1.074100392519842</v>
+        <v>1.074100392544137</v>
       </c>
       <c r="AI2">
-        <v>1.084123437159987</v>
+        <v>1.084123437129621</v>
       </c>
       <c r="AJ2">
-        <v>0.9026261131934777</v>
+        <v>0.9026261132009109</v>
       </c>
       <c r="AK2">
-        <v>1.030865258692281</v>
+        <v>1.030865258709721</v>
       </c>
       <c r="AL2">
-        <v>1.161791479682332</v>
+        <v>1.161791479652922</v>
       </c>
       <c r="AM2">
-        <v>-1.024983324859656</v>
+        <v>-1.024983325969495</v>
       </c>
       <c r="AN2">
-        <v>-118.1612950286639</v>
+        <v>-118.1612950275836</v>
       </c>
       <c r="AO2">
-        <v>117.8780975574395</v>
+        <v>117.8780975579064</v>
       </c>
       <c r="AP2">
-        <v>5.107911107042167</v>
+        <v>5.107911106272772</v>
       </c>
       <c r="AQ2">
-        <v>-121.6768947899944</v>
+        <v>-121.6768947886682</v>
       </c>
       <c r="AR2">
-        <v>117.7717215282353</v>
+        <v>117.7717215283778</v>
       </c>
     </row>
   </sheetData>
@@ -3297,7 +3297,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006854930371393699</v>
+        <v>0.0006854930371394039</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.0006853752963058902</v>
+        <v>0.000685375296305924</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3315,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.007915391790400588</v>
+        <v>0.00791539179040098</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.007914032236362506</v>
+        <v>0.007914032236362896</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3333,43 +3333,43 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.005872510878274144</v>
+        <v>0.005872510878275351</v>
       </c>
       <c r="O2">
-        <v>2.490613706900159E-06</v>
+        <v>2.490613705522699E-06</v>
       </c>
       <c r="P2">
-        <v>-1.946148760479355E-06</v>
+        <v>-1.94614876010642E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.005872313457091085</v>
+        <v>-0.005872313457091281</v>
       </c>
       <c r="R2">
-        <v>3.943163922268305E-13</v>
+        <v>3.943171401881212E-13</v>
       </c>
       <c r="S2">
-        <v>-7.346806955561341E-13</v>
+        <v>-7.346856939587474E-13</v>
       </c>
       <c r="T2">
-        <v>0.005880412584957588</v>
+        <v>0.005880412584957151</v>
       </c>
       <c r="U2">
-        <v>-8.090817185236826E-07</v>
+        <v>-8.090817188938578E-07</v>
       </c>
       <c r="V2">
-        <v>-1.752376420264074E-06</v>
+        <v>-1.752376418894082E-06</v>
       </c>
       <c r="W2">
-        <v>-0.00587743659068571</v>
+        <v>-0.00587743659068628</v>
       </c>
       <c r="X2">
-        <v>-6.206030118298629E-13</v>
+        <v>-6.206041447945707E-13</v>
       </c>
       <c r="Y2">
-        <v>-3.122796730498063E-14</v>
+        <v>-3.12217385368909E-14</v>
       </c>
       <c r="Z2">
-        <v>-45.04223654033806</v>
+        <v>-45.04223654033096</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>134.9729004244464</v>
+        <v>134.9729004244437</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3387,40 +3387,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.04992576210003</v>
+        <v>1.049925762100047</v>
       </c>
       <c r="AH2">
-        <v>1.049965338349732</v>
+        <v>1.049965338349739</v>
       </c>
       <c r="AI2">
-        <v>1.050007307828673</v>
+        <v>1.05000730782865</v>
       </c>
       <c r="AJ2">
-        <v>1.049822451773757</v>
+        <v>1.049822451773774</v>
       </c>
       <c r="AK2">
-        <v>1.049965809890551</v>
+        <v>1.049965809890557</v>
       </c>
       <c r="AL2">
-        <v>1.05006355719792</v>
+        <v>1.050063557197897</v>
       </c>
       <c r="AM2">
-        <v>-0.00371553940644005</v>
+        <v>-0.003715539407356725</v>
       </c>
       <c r="AN2">
-        <v>-119.9993729066301</v>
+        <v>-119.9993729066289</v>
       </c>
       <c r="AO2">
-        <v>119.9980507302622</v>
+        <v>119.9980507302618</v>
       </c>
       <c r="AP2">
-        <v>-0.002117434391226924</v>
+        <v>-0.00211743439214438</v>
       </c>
       <c r="AQ2">
-        <v>-120.0029320926467</v>
+        <v>-120.0029320926454</v>
       </c>
       <c r="AR2">
-        <v>119.9998524820383</v>
+        <v>119.999852482038</v>
       </c>
     </row>
   </sheetData>
@@ -3509,10 +3509,10 @@
         <v>27.99598820975723</v>
       </c>
       <c r="H2">
-        <v>3.520383623275721</v>
+        <v>3.520383623275714</v>
       </c>
       <c r="I2">
-        <v>-2.501475639660094</v>
+        <v>-2.501475639660088</v>
       </c>
       <c r="J2">
         <v>26.04543822501815</v>
@@ -3521,10 +3521,10 @@
         <v>-24.8893695681453</v>
       </c>
       <c r="L2">
-        <v>-83.04041303320911</v>
+        <v>-83.04041303320912</v>
       </c>
       <c r="M2">
-        <v>96.9595869667836</v>
+        <v>96.95958696678359</v>
       </c>
       <c r="N2">
         <v>0.9387871686719225</v>
@@ -3533,7 +3533,7 @@
         <v>0.8935122209065726</v>
       </c>
       <c r="P2">
-        <v>-0.7380414197227492</v>
+        <v>-0.7380414197227488</v>
       </c>
       <c r="Q2">
         <v>1.22041676695381</v>
@@ -3688,7 +3688,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0007181173646759844</v>
+        <v>0.0007181173646760196</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.0007179940202618587</v>
+        <v>0.0007179940202618942</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.008292105076108485</v>
+        <v>0.008292105076108893</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.008290680817494515</v>
+        <v>0.008290680817494924</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3724,43 +3724,43 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.006444817177845587</v>
+        <v>0.006444817177846915</v>
       </c>
       <c r="O2">
-        <v>2.733412002840775E-06</v>
+        <v>2.733412001332782E-06</v>
       </c>
       <c r="P2">
-        <v>-2.135815411205648E-06</v>
+        <v>-2.135815410807409E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.006444600591469879</v>
+        <v>-0.006444600591470104</v>
       </c>
       <c r="R2">
-        <v>4.327671140314762E-13</v>
+        <v>4.327645305318723E-13</v>
       </c>
       <c r="S2">
-        <v>-8.062997438185676E-13</v>
+        <v>-8.062959500345618E-13</v>
       </c>
       <c r="T2">
-        <v>0.006453756771154004</v>
+        <v>0.006453756771153518</v>
       </c>
       <c r="U2">
-        <v>-8.87892620885661E-07</v>
+        <v>-8.878926212943549E-07</v>
       </c>
       <c r="V2">
-        <v>-1.923238759725732E-06</v>
+        <v>-1.923238758211964E-06</v>
       </c>
       <c r="W2">
-        <v>-0.006450490707074807</v>
+        <v>-0.006450490707075426</v>
       </c>
       <c r="X2">
-        <v>-6.810893493228039E-13</v>
+        <v>-6.810849197113239E-13</v>
       </c>
       <c r="Y2">
-        <v>-3.428770337636365E-14</v>
+        <v>-3.428918558882281E-14</v>
       </c>
       <c r="Z2">
-        <v>-45.04342524576477</v>
+        <v>-45.04342524575762</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -3769,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>134.9717117190197</v>
+        <v>134.971711719017</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3778,40 +3778,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.099922301247776</v>
+        <v>1.099922301247794</v>
       </c>
       <c r="AH2">
-        <v>1.099963762759872</v>
+        <v>1.099963762759879</v>
       </c>
       <c r="AI2">
-        <v>1.10000772864506</v>
+        <v>1.100007728645036</v>
       </c>
       <c r="AJ2">
-        <v>1.099814074761364</v>
+        <v>1.099814074761381</v>
       </c>
       <c r="AK2">
-        <v>1.099964255324837</v>
+        <v>1.099964255324844</v>
       </c>
       <c r="AL2">
-        <v>1.100066655780067</v>
+        <v>1.100066655780043</v>
       </c>
       <c r="AM2">
-        <v>-0.00371536100334628</v>
+        <v>-0.003715361004262948</v>
       </c>
       <c r="AN2">
-        <v>-119.9993728833771</v>
+        <v>-119.9993728833759</v>
       </c>
       <c r="AO2">
-        <v>119.9980507714612</v>
+        <v>119.9980507714609</v>
       </c>
       <c r="AP2">
-        <v>-0.002117179605902045</v>
+        <v>-0.002117179606819498</v>
       </c>
       <c r="AQ2">
-        <v>-120.0029319794943</v>
+        <v>-120.0029319794931</v>
       </c>
       <c r="AR2">
-        <v>119.9998524137853</v>
+        <v>119.999852413785</v>
       </c>
     </row>
   </sheetData>
@@ -3963,16 +3963,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.6856965116168104</v>
+        <v>0.6856965116308615</v>
       </c>
       <c r="C2">
-        <v>0.0003674656442047039</v>
+        <v>0.0003674656441008979</v>
       </c>
       <c r="D2">
-        <v>0.0003674656442049241</v>
+        <v>0.0003674656441004521</v>
       </c>
       <c r="E2">
-        <v>0.6855778737121017</v>
+        <v>0.685577873726151</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3981,16 +3981,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>7.917741311287058</v>
+        <v>7.917741311449305</v>
       </c>
       <c r="I2">
-        <v>0.004243127771990501</v>
+        <v>0.004243127770791853</v>
       </c>
       <c r="J2">
-        <v>0.004243127771993043</v>
+        <v>0.004243127770786705</v>
       </c>
       <c r="K2">
-        <v>7.916371398762664</v>
+        <v>7.916371398924891</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3999,52 +3999,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.023877767655255</v>
+        <v>2.023877767363213</v>
       </c>
       <c r="O2">
-        <v>0.003494818838173359</v>
+        <v>0.003494818837275781</v>
       </c>
       <c r="P2">
-        <v>-0.0004840648036564087</v>
+        <v>-0.0004840648036147889</v>
       </c>
       <c r="Q2">
-        <v>-0.6016217617435231</v>
+        <v>-0.6016217613922148</v>
       </c>
       <c r="R2">
-        <v>8.604037205146534E-10</v>
+        <v>8.60402455296008E-10</v>
       </c>
       <c r="S2">
-        <v>-1.306590878470301E-09</v>
+        <v>-1.30658655117427E-09</v>
       </c>
       <c r="T2">
-        <v>6.401781929084196</v>
+        <v>6.401781929346476</v>
       </c>
       <c r="U2">
-        <v>0.001781525018729856</v>
+        <v>0.001781525018224845</v>
       </c>
       <c r="V2">
-        <v>-0.003955606200147019</v>
+        <v>-0.003955606198899018</v>
       </c>
       <c r="W2">
-        <v>-5.986061110871757</v>
+        <v>-5.986061111117255</v>
       </c>
       <c r="X2">
-        <v>-7.360294098938284E-10</v>
+        <v>-7.360294572973848E-10</v>
       </c>
       <c r="Y2">
-        <v>-5.150814592994449E-10</v>
+        <v>-5.150898299016974E-10</v>
       </c>
       <c r="Z2">
-        <v>-74.10760494852499</v>
+        <v>-74.10760495265019</v>
       </c>
       <c r="AA2">
-        <v>-145.2574568257926</v>
+        <v>-145.2574568239959</v>
       </c>
       <c r="AB2">
-        <v>-145.2574568258553</v>
+        <v>-145.257456823977</v>
       </c>
       <c r="AC2">
-        <v>105.9214581648889</v>
+        <v>105.9214581607538</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4053,40 +4053,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8479794220226501</v>
+        <v>0.8479794220257398</v>
       </c>
       <c r="AH2">
-        <v>0.9244835647268543</v>
+        <v>0.9244835647454973</v>
       </c>
       <c r="AI2">
-        <v>0.9391927160122762</v>
+        <v>0.9391927159861561</v>
       </c>
       <c r="AJ2">
-        <v>0.7599716430920095</v>
+        <v>0.7599716431028537</v>
       </c>
       <c r="AK2">
-        <v>0.8553246078420971</v>
+        <v>0.8553246078496856</v>
       </c>
       <c r="AL2">
-        <v>1.06093302872816</v>
+        <v>1.060933028703993</v>
       </c>
       <c r="AM2">
-        <v>-1.651583920867921</v>
+        <v>-1.651583921942175</v>
       </c>
       <c r="AN2">
-        <v>-118.2467086490417</v>
+        <v>-118.2467086478626</v>
       </c>
       <c r="AO2">
-        <v>117.7656976575536</v>
+        <v>117.7656976578465</v>
       </c>
       <c r="AP2">
-        <v>10.18228784250199</v>
+        <v>10.18228784192967</v>
       </c>
       <c r="AQ2">
-        <v>-124.7234951065675</v>
+        <v>-124.7234951049988</v>
       </c>
       <c r="AR2">
-        <v>117.3371175649171</v>
+        <v>117.3371175646854</v>
       </c>
     </row>
   </sheetData>
@@ -4238,16 +4238,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.6496072124744963</v>
+        <v>0.6496072124878087</v>
       </c>
       <c r="C2">
-        <v>0.0003481253422879027</v>
+        <v>0.0003481253421893713</v>
       </c>
       <c r="D2">
-        <v>0.0003481253422875847</v>
+        <v>0.0003481253421887032</v>
       </c>
       <c r="E2">
-        <v>0.6494948186716023</v>
+        <v>0.6494948186849133</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4256,16 +4256,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>7.501017979793457</v>
+        <v>7.501017979947176</v>
       </c>
       <c r="I2">
-        <v>0.004019805201633026</v>
+        <v>0.004019805200495282</v>
       </c>
       <c r="J2">
-        <v>0.004019805201629353</v>
+        <v>0.004019805200487568</v>
       </c>
       <c r="K2">
-        <v>7.499720167946336</v>
+        <v>7.499720168100039</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4274,52 +4274,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.816444261592665</v>
+        <v>1.81644426133056</v>
       </c>
       <c r="O2">
-        <v>0.003136624022144557</v>
+        <v>0.003136624021337632</v>
       </c>
       <c r="P2">
-        <v>-0.0004344515014160482</v>
+        <v>-0.0004344515013774529</v>
       </c>
       <c r="Q2">
-        <v>-0.539959682463611</v>
+        <v>-0.5399596821483114</v>
       </c>
       <c r="R2">
-        <v>7.722155564878141E-10</v>
+        <v>7.722167863679312E-10</v>
       </c>
       <c r="S2">
-        <v>-1.172674334165018E-09</v>
+        <v>-1.172669997184933E-09</v>
       </c>
       <c r="T2">
-        <v>5.745643454804426</v>
+        <v>5.745643455039832</v>
       </c>
       <c r="U2">
-        <v>0.001598930997157195</v>
+        <v>0.001598930996702367</v>
       </c>
       <c r="V2">
-        <v>-0.003550183859027544</v>
+        <v>-0.003550183857908554</v>
       </c>
       <c r="W2">
-        <v>-5.372531151910047</v>
+        <v>-5.37253115213039</v>
       </c>
       <c r="X2">
-        <v>-6.605933394161205E-10</v>
+        <v>-6.605915648196474E-10</v>
       </c>
       <c r="Y2">
-        <v>-4.622900107276266E-10</v>
+        <v>-4.622958081582726E-10</v>
       </c>
       <c r="Z2">
-        <v>-74.10760494852499</v>
+        <v>-74.10760495265016</v>
       </c>
       <c r="AA2">
-        <v>-145.2574568258104</v>
+        <v>-145.2574568240024</v>
       </c>
       <c r="AB2">
-        <v>-145.2574568258563</v>
+        <v>-145.2574568239981</v>
       </c>
       <c r="AC2">
-        <v>105.9214581648889</v>
+        <v>105.9214581607538</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4328,40 +4328,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8033489149259427</v>
+        <v>0.8033489149288698</v>
       </c>
       <c r="AH2">
-        <v>0.8758265227930835</v>
+        <v>0.8758265228107448</v>
       </c>
       <c r="AI2">
-        <v>0.8897615080270886</v>
+        <v>0.8897615080023419</v>
       </c>
       <c r="AJ2">
-        <v>0.7199731255225486</v>
+        <v>0.7199731255328221</v>
       </c>
       <c r="AK2">
-        <v>0.8103075119210269</v>
+        <v>0.8103075119282183</v>
       </c>
       <c r="AL2">
-        <v>1.005094434255147</v>
+        <v>1.005094434232251</v>
       </c>
       <c r="AM2">
-        <v>-1.651583920867922</v>
+        <v>-1.651583921942174</v>
       </c>
       <c r="AN2">
-        <v>-118.2467086490401</v>
+        <v>-118.2467086478626</v>
       </c>
       <c r="AO2">
-        <v>117.765697657552</v>
+        <v>117.7656976578465</v>
       </c>
       <c r="AP2">
-        <v>10.18228784250197</v>
+        <v>10.18228784192967</v>
       </c>
       <c r="AQ2">
-        <v>-124.7234951065657</v>
+        <v>-124.7234951049988</v>
       </c>
       <c r="AR2">
-        <v>117.3371175649156</v>
+        <v>117.3371175646854</v>
       </c>
     </row>
   </sheetData>
@@ -4513,7 +4513,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006201541664570217</v>
+        <v>0.0006201541664570514</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.0006200468685640646</v>
+        <v>0.000620046868564094</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.00716092349886059</v>
+        <v>0.007160923498860933</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.007159684529512944</v>
+        <v>0.007159684529513283</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4549,43 +4549,43 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.004805774700650251</v>
+        <v>0.004805774700651232</v>
       </c>
       <c r="O2">
-        <v>3.637549493174973E-06</v>
+        <v>3.637549492048337E-06</v>
       </c>
       <c r="P2">
-        <v>-2.027977187532186E-06</v>
+        <v>-2.027977187235056E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.004806218452019323</v>
+        <v>-0.004806218452019475</v>
       </c>
       <c r="R2">
-        <v>4.82796406082423E-13</v>
+        <v>4.827958667706141E-13</v>
       </c>
       <c r="S2">
-        <v>-1.133408904699081E-12</v>
+        <v>-1.133405333592121E-12</v>
       </c>
       <c r="T2">
-        <v>0.004814231908725504</v>
+        <v>0.004814231908725138</v>
       </c>
       <c r="U2">
-        <v>-2.41302180467538E-07</v>
+        <v>-2.413021807731823E-07</v>
       </c>
       <c r="V2">
-        <v>-3.029590458881125E-06</v>
+        <v>-3.029590457745388E-06</v>
       </c>
       <c r="W2">
-        <v>-0.004810622747828308</v>
+        <v>-0.004810622747828766</v>
       </c>
       <c r="X2">
-        <v>-1.029778824039081E-12</v>
+        <v>-1.029777561116034E-12</v>
       </c>
       <c r="Y2">
-        <v>9.666257033206314E-14</v>
+        <v>9.665638513248272E-14</v>
       </c>
       <c r="Z2">
-        <v>-45.05424767794447</v>
+        <v>-45.05424767793736</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -4594,7 +4594,7 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>134.9748154354694</v>
+        <v>134.9748154354666</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4603,40 +4603,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9499297874479908</v>
+        <v>0.949929787448006</v>
       </c>
       <c r="AH2">
-        <v>0.9499670492871076</v>
+        <v>0.9499670492871134</v>
       </c>
       <c r="AI2">
-        <v>0.9500069615282928</v>
+        <v>0.950006961528272</v>
       </c>
       <c r="AJ2">
-        <v>0.9497812803227218</v>
+        <v>0.949781280322737</v>
       </c>
       <c r="AK2">
-        <v>0.9499537799874793</v>
+        <v>0.949953779987485</v>
       </c>
       <c r="AL2">
-        <v>0.9501084357581588</v>
+        <v>0.9501084357581381</v>
       </c>
       <c r="AM2">
-        <v>-0.00387742104126196</v>
+        <v>-0.003877421042180979</v>
       </c>
       <c r="AN2">
-        <v>-119.9993386200579</v>
+        <v>-119.9993386200566</v>
       </c>
       <c r="AO2">
-        <v>119.9979489019564</v>
+        <v>119.997948901956</v>
       </c>
       <c r="AP2">
-        <v>0.0010556050580968</v>
+        <v>0.00105560505717654</v>
       </c>
       <c r="AQ2">
-        <v>-120.0059435705164</v>
+        <v>-120.0059435705151</v>
       </c>
       <c r="AR2">
-        <v>120.0005578078755</v>
+        <v>120.0005578078752</v>
       </c>
     </row>
   </sheetData>
@@ -4788,7 +4788,7 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.000587514465294116</v>
+        <v>0.0005875144652941445</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.0005874128146601001</v>
+        <v>0.0005874128146601284</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.006784032693807139</v>
+        <v>0.006784032693807467</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4815,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.006782858933388891</v>
+        <v>0.006782858933389218</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4824,43 +4824,43 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.004313215954546879</v>
+        <v>0.004313215954547761</v>
       </c>
       <c r="O2">
-        <v>3.264725769872404E-06</v>
+        <v>3.264725768862394E-06</v>
       </c>
       <c r="P2">
-        <v>-1.820123519217541E-06</v>
+        <v>-1.820123518953225E-06</v>
       </c>
       <c r="Q2">
-        <v>-0.004313614224462584</v>
+        <v>-0.004313614224462723</v>
       </c>
       <c r="R2">
-        <v>4.333131143981972E-13</v>
+        <v>4.333115625007985E-13</v>
       </c>
       <c r="S2">
-        <v>-1.017243102626474E-12</v>
+        <v>-1.017239078228601E-12</v>
       </c>
       <c r="T2">
-        <v>0.004320806357150679</v>
+        <v>0.004320806357150355</v>
       </c>
       <c r="U2">
-        <v>-2.165703719986742E-07</v>
+        <v>-2.165703722711592E-07</v>
       </c>
       <c r="V2">
-        <v>-2.719078341565819E-06</v>
+        <v>-2.71907834054755E-06</v>
       </c>
       <c r="W2">
-        <v>-0.004317567110341584</v>
+        <v>-0.004317567110341999</v>
       </c>
       <c r="X2">
-        <v>-9.242330610831759E-13</v>
+        <v>-9.242336672115881E-13</v>
       </c>
       <c r="Y2">
-        <v>8.675403894854241E-14</v>
+        <v>8.674915051436066E-14</v>
       </c>
       <c r="Z2">
-        <v>-45.05424767794445</v>
+        <v>-45.05424767793736</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>134.9748154354694</v>
+        <v>134.9748154354666</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4878,40 +4878,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.899933470298046</v>
+        <v>0.8999334702980605</v>
       </c>
       <c r="AH2">
-        <v>0.8999687709872435</v>
+        <v>0.8999687709872488</v>
       </c>
       <c r="AI2">
-        <v>0.9000065825836284</v>
+        <v>0.9000065825836087</v>
       </c>
       <c r="AJ2">
-        <v>0.8997927793392265</v>
+        <v>0.8997927793392408</v>
       </c>
       <c r="AK2">
-        <v>0.8999562000719814</v>
+        <v>0.8999562000719866</v>
       </c>
       <c r="AL2">
-        <v>0.9001027160632138</v>
+        <v>0.9001027160631941</v>
       </c>
       <c r="AM2">
-        <v>-0.003877421041261959</v>
+        <v>-0.003877421042180981</v>
       </c>
       <c r="AN2">
-        <v>-119.9993386200579</v>
+        <v>-119.9993386200567</v>
       </c>
       <c r="AO2">
-        <v>119.9979489019564</v>
+        <v>119.997948901956</v>
       </c>
       <c r="AP2">
-        <v>0.001055605058096797</v>
+        <v>0.001055605057176538</v>
       </c>
       <c r="AQ2">
-        <v>-120.0059435705164</v>
+        <v>-120.0059435705151</v>
       </c>
       <c r="AR2">
-        <v>120.0005578078755</v>
+        <v>120.0005578078752</v>
       </c>
     </row>
   </sheetData>
@@ -5063,130 +5063,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0002564554848479049</v>
+        <v>0.0002564554847442322</v>
       </c>
       <c r="C2">
-        <v>0.8523745307818362</v>
+        <v>0.8523745307411077</v>
       </c>
       <c r="D2">
-        <v>0.7531280967062552</v>
+        <v>0.753128096770816</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8524648921973315</v>
+        <v>0.8524648921565173</v>
       </c>
       <c r="G2">
-        <v>0.7528746743527788</v>
+        <v>0.7528746744174506</v>
       </c>
       <c r="H2">
-        <v>0.002961292864241878</v>
+        <v>0.002961292863044769</v>
       </c>
       <c r="I2">
-        <v>9.842373295945483</v>
+        <v>9.842373295475189</v>
       </c>
       <c r="J2">
-        <v>8.696374187352539</v>
+        <v>8.696374188098023</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>9.843416699696693</v>
+        <v>9.843416699225413</v>
       </c>
       <c r="M2">
-        <v>8.693447918072573</v>
+        <v>8.69344791881934</v>
       </c>
       <c r="N2">
-        <v>0.001970371953170221</v>
+        <v>0.001970371952133629</v>
       </c>
       <c r="O2">
-        <v>1.859636239896814</v>
+        <v>1.859636239400057</v>
       </c>
       <c r="P2">
-        <v>1.088803611030678</v>
+        <v>1.088803611105361</v>
       </c>
       <c r="Q2">
-        <v>-2.843007804863957E-11</v>
+        <v>-2.847471517427907E-11</v>
       </c>
       <c r="R2">
-        <v>-0.8855525027902816</v>
+        <v>-0.8855525023770531</v>
       </c>
       <c r="S2">
-        <v>-0.6907273146012022</v>
+        <v>-0.6907273145180408</v>
       </c>
       <c r="T2">
-        <v>-0.002240894357497427</v>
+        <v>-0.002240894356760101</v>
       </c>
       <c r="U2">
-        <v>8.767827937809322</v>
+        <v>8.767827937317294</v>
       </c>
       <c r="V2">
-        <v>7.875053586301765</v>
+        <v>7.875053587162347</v>
       </c>
       <c r="W2">
-        <v>-8.723532357859254E-10</v>
+        <v>-8.723500158057014E-10</v>
       </c>
       <c r="X2">
-        <v>-8.811135961520074</v>
+        <v>-8.811135961122586</v>
       </c>
       <c r="Y2">
-        <v>-6.872650785409242</v>
+        <v>-6.872650786142977</v>
       </c>
       <c r="Z2">
-        <v>48.17161566266029</v>
+        <v>48.17161567015857</v>
       </c>
       <c r="AA2">
-        <v>158.7945129824514</v>
+        <v>158.79451297901</v>
       </c>
       <c r="AB2">
-        <v>39.35227780653889</v>
+        <v>39.35227780574499</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-21.18935471169926</v>
+        <v>-21.18935471514531</v>
       </c>
       <c r="AE2">
-        <v>-140.6507145238157</v>
+        <v>-140.650714524611</v>
       </c>
       <c r="AG2">
-        <v>1.00765197596869</v>
+        <v>1.007651975957906</v>
       </c>
       <c r="AH2">
-        <v>0.91064122141542</v>
+        <v>0.9106412213995578</v>
       </c>
       <c r="AI2">
-        <v>0.9141702059329015</v>
+        <v>0.9141702059537381</v>
       </c>
       <c r="AJ2">
-        <v>1.049740590307744</v>
+        <v>1.049740590286838</v>
       </c>
       <c r="AK2">
-        <v>0.8996393334544833</v>
+        <v>0.8996393334531793</v>
       </c>
       <c r="AL2">
-        <v>0.7945379080495687</v>
+        <v>0.7945379080643393</v>
       </c>
       <c r="AM2">
-        <v>-0.5038879970922923</v>
+        <v>-0.5038879951929024</v>
       </c>
       <c r="AN2">
-        <v>-123.1803309428236</v>
+        <v>-123.1803309438111</v>
       </c>
       <c r="AO2">
-        <v>121.4804781525188</v>
+        <v>121.4804781520411</v>
       </c>
       <c r="AP2">
-        <v>-4.125965106835047</v>
+        <v>-4.125965105571667</v>
       </c>
       <c r="AQ2">
-        <v>-116.9285253120398</v>
+        <v>-116.9285253130829</v>
       </c>
       <c r="AR2">
-        <v>123.6101156463006</v>
+        <v>123.6101156468002</v>
       </c>
     </row>
   </sheetData>
@@ -5338,130 +5338,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0002587216661832632</v>
+        <v>0.0002587216660753406</v>
       </c>
       <c r="C2">
-        <v>0.8582140563355397</v>
+        <v>0.8582140562955471</v>
       </c>
       <c r="D2">
-        <v>0.7618365395549876</v>
+        <v>0.7618365396176315</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.8583061493100907</v>
+        <v>0.8583061492700105</v>
       </c>
       <c r="G2">
-        <v>0.7615807181534057</v>
+        <v>0.7615807182161625</v>
       </c>
       <c r="H2">
-        <v>0.002987460472321911</v>
+        <v>0.002987460471075727</v>
       </c>
       <c r="I2">
-        <v>9.909802328952891</v>
+        <v>9.909802328491097</v>
       </c>
       <c r="J2">
-        <v>8.796930623811303</v>
+        <v>8.796930624534651</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>9.91086572702584</v>
+        <v>9.910865726563035</v>
       </c>
       <c r="M2">
-        <v>8.793976652709945</v>
+        <v>8.7939766534346</v>
       </c>
       <c r="N2">
-        <v>0.002101451536032052</v>
+        <v>0.002101451534851921</v>
       </c>
       <c r="O2">
-        <v>1.927175079457686</v>
+        <v>1.927175078955169</v>
       </c>
       <c r="P2">
-        <v>1.150289328368994</v>
+        <v>1.150289328438713</v>
       </c>
       <c r="Q2">
-        <v>-2.192924981761149E-11</v>
+        <v>-2.191943827661001E-11</v>
       </c>
       <c r="R2">
-        <v>-0.9404790914308929</v>
+        <v>-0.9404790910116846</v>
       </c>
       <c r="S2">
-        <v>-0.7404513340556633</v>
+        <v>-0.7404513339705279</v>
       </c>
       <c r="T2">
-        <v>-0.002357840794419367</v>
+        <v>-0.002357840793664265</v>
       </c>
       <c r="U2">
-        <v>9.310415662364237</v>
+        <v>9.310415661852216</v>
       </c>
       <c r="V2">
-        <v>8.390956284426789</v>
+        <v>8.390956285308562</v>
       </c>
       <c r="W2">
-        <v>-9.217351519291054E-10</v>
+        <v>-9.217253949975268E-10</v>
       </c>
       <c r="X2">
-        <v>-9.357648604239975</v>
+        <v>-9.357648603820246</v>
       </c>
       <c r="Y2">
-        <v>-7.367398585509607</v>
+        <v>-7.367398586268028</v>
       </c>
       <c r="Z2">
-        <v>47.82033816353203</v>
+        <v>47.82033817221855</v>
       </c>
       <c r="AA2">
-        <v>158.6641885070935</v>
+        <v>158.6641885038014</v>
       </c>
       <c r="AB2">
-        <v>39.23461788386736</v>
+        <v>39.23461788306118</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-21.31967097132118</v>
+        <v>-21.31967097461794</v>
       </c>
       <c r="AE2">
-        <v>-140.7682879290835</v>
+        <v>-140.7682879298913</v>
       </c>
       <c r="AG2">
-        <v>1.057220132949625</v>
+        <v>1.057220132939108</v>
       </c>
       <c r="AH2">
-        <v>0.9594316558502342</v>
+        <v>0.9594316558340692</v>
       </c>
       <c r="AI2">
-        <v>0.962771493731883</v>
+        <v>0.9627714937531007</v>
       </c>
       <c r="AJ2">
-        <v>1.099169388014615</v>
+        <v>1.099169387994137</v>
       </c>
       <c r="AK2">
-        <v>0.9489373552478196</v>
+        <v>0.9489373552457646</v>
       </c>
       <c r="AL2">
-        <v>0.8419983885064033</v>
+        <v>0.8419983885218627</v>
       </c>
       <c r="AM2">
-        <v>-0.4702887485894148</v>
+        <v>-0.4702887467708716</v>
       </c>
       <c r="AN2">
-        <v>-123.0303866289149</v>
+        <v>-123.030386629867</v>
       </c>
       <c r="AO2">
-        <v>121.4287781094674</v>
+        <v>121.4287781090041</v>
       </c>
       <c r="AP2">
-        <v>-3.973958576462286</v>
+        <v>-3.973958575225485</v>
       </c>
       <c r="AQ2">
-        <v>-117.0588415729329</v>
+        <v>-117.0588415739443</v>
       </c>
       <c r="AR2">
-        <v>123.4925422388043</v>
+        <v>123.4925422392388</v>
       </c>
     </row>
   </sheetData>
@@ -5616,127 +5616,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.000685318873865615</v>
+        <v>0.0006853188738657028</v>
       </c>
       <c r="D2">
-        <v>0.0006855686975861112</v>
+        <v>0.0006855686975860554</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0006854168122596297</v>
+        <v>0.0006854168122596156</v>
       </c>
       <c r="G2">
-        <v>0.0006853530088091373</v>
+        <v>0.0006853530088091835</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.007913380726140881</v>
+        <v>0.007913380726141894</v>
       </c>
       <c r="J2">
-        <v>0.00791626544198645</v>
+        <v>0.007916265441985806</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007914511621303848</v>
+        <v>0.007914511621303686</v>
       </c>
       <c r="M2">
-        <v>0.007913774882517507</v>
+        <v>0.007913774882518041</v>
       </c>
       <c r="N2">
-        <v>5.443852494621999E-07</v>
+        <v>5.443852485029782E-07</v>
       </c>
       <c r="O2">
-        <v>0.005871146686170121</v>
+        <v>0.005871146686171097</v>
       </c>
       <c r="P2">
-        <v>0.005874251506046535</v>
+        <v>0.005874251506046745</v>
       </c>
       <c r="Q2">
-        <v>-3.403454416305276E-13</v>
+        <v>-3.403940151180586E-13</v>
       </c>
       <c r="R2">
-        <v>-0.005873024898188756</v>
+        <v>-0.00587302489818836</v>
       </c>
       <c r="S2">
-        <v>-0.005871931542926474</v>
+        <v>-0.005871931542927051</v>
       </c>
       <c r="T2">
-        <v>-2.561469466649004E-06</v>
+        <v>-2.561469465643512E-06</v>
       </c>
       <c r="U2">
-        <v>0.005878873093673323</v>
+        <v>0.005878873093673782</v>
       </c>
       <c r="V2">
-        <v>0.005879583062032849</v>
+        <v>0.005879583062031945</v>
       </c>
       <c r="W2">
-        <v>-6.517910915022503E-13</v>
+        <v>-6.517886602108348E-13</v>
       </c>
       <c r="X2">
-        <v>-0.005878148651693955</v>
+        <v>-0.005878148651694041</v>
       </c>
       <c r="Y2">
-        <v>-0.005877054344383406</v>
+        <v>-0.00587705434438388</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-165.0433408144911</v>
+        <v>-165.0433408144899</v>
       </c>
       <c r="AB2">
-        <v>74.97092240180703</v>
+        <v>74.97092240181279</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>14.97275273741624</v>
+        <v>14.97275273741264</v>
       </c>
       <c r="AE2">
-        <v>-105.0300318461375</v>
+        <v>-105.0300318461367</v>
       </c>
       <c r="AG2">
-        <v>1.049972695538359</v>
+        <v>1.049972695538342</v>
       </c>
       <c r="AH2">
-        <v>1.049933113192323</v>
+        <v>1.049933113192316</v>
       </c>
       <c r="AI2">
-        <v>1.049891144249224</v>
+        <v>1.049891144249247</v>
       </c>
       <c r="AJ2">
-        <v>1.05002941711669</v>
+        <v>1.050029417116674</v>
       </c>
       <c r="AK2">
-        <v>1.049886043696695</v>
+        <v>1.049886043696688</v>
       </c>
       <c r="AL2">
-        <v>1.049788312913531</v>
+        <v>1.049788312913553</v>
       </c>
       <c r="AM2">
-        <v>-0.001322287862133719</v>
+        <v>-0.001322287861216035</v>
       </c>
       <c r="AN2">
-        <v>-120.0056650926456</v>
+        <v>-120.0056650926469</v>
       </c>
       <c r="AO2">
-        <v>119.9969118466568</v>
+        <v>119.9969118466572</v>
       </c>
       <c r="AP2">
-        <v>-0.003079264980204504</v>
+        <v>-0.003079264979286373</v>
       </c>
       <c r="AQ2">
-        <v>-120.0022651251549</v>
+        <v>-120.0022651251561</v>
       </c>
       <c r="AR2">
-        <v>119.9949503001408</v>
+        <v>119.9949503001411</v>
       </c>
     </row>
   </sheetData>
@@ -5891,127 +5891,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0007179349113930541</v>
+        <v>0.0007179349113931489</v>
       </c>
       <c r="D2">
-        <v>0.0007181966258240186</v>
+        <v>0.0007181966258239602</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0007180375109202149</v>
+        <v>0.000718037510920203</v>
       </c>
       <c r="G2">
-        <v>0.000717970671878429</v>
+        <v>0.0007179706718784767</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.008289998287068197</v>
+        <v>0.008289998287069293</v>
       </c>
       <c r="J2">
-        <v>0.008293020305011561</v>
+        <v>0.008293020305010888</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.0082911830043607</v>
+        <v>0.008291183004360561</v>
       </c>
       <c r="M2">
-        <v>0.00829041121358535</v>
+        <v>0.0082904112135859</v>
       </c>
       <c r="N2">
-        <v>5.97509126257617E-07</v>
+        <v>5.975091251350517E-07</v>
       </c>
       <c r="O2">
-        <v>0.006443320013886501</v>
+        <v>0.006443320013887598</v>
       </c>
       <c r="P2">
-        <v>0.006446727512777074</v>
+        <v>0.006446727512777331</v>
       </c>
       <c r="Q2">
-        <v>-3.735095693235421E-13</v>
+        <v>-3.734923948053935E-13</v>
       </c>
       <c r="R2">
-        <v>-0.006445381345633723</v>
+        <v>-0.006445381345633308</v>
       </c>
       <c r="S2">
-        <v>-0.006444181454770906</v>
+        <v>-0.006444181454771561</v>
       </c>
       <c r="T2">
-        <v>-2.811143819331379E-06</v>
+        <v>-2.811143818232206E-06</v>
       </c>
       <c r="U2">
-        <v>0.00645206717871324</v>
+        <v>0.006452067178713772</v>
       </c>
       <c r="V2">
-        <v>0.006452846422938139</v>
+        <v>0.006452846422937118</v>
       </c>
       <c r="W2">
-        <v>-7.153368330182831E-13</v>
+        <v>-7.153317452761826E-13</v>
       </c>
       <c r="X2">
-        <v>-0.006451272173973753</v>
+        <v>-0.006451272173973882</v>
       </c>
       <c r="Y2">
-        <v>-0.006450071188458154</v>
+        <v>-0.006450071188458638</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-165.0445295882011</v>
+        <v>-165.0445295881998</v>
       </c>
       <c r="AB2">
-        <v>74.96973380949017</v>
+        <v>74.96973380949618</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>14.97156396376468</v>
+        <v>14.97156396376102</v>
       </c>
       <c r="AE2">
-        <v>-105.0312204384066</v>
+        <v>-105.0312204384055</v>
       </c>
       <c r="AG2">
-        <v>1.099971469318982</v>
+        <v>1.099971469318964</v>
       </c>
       <c r="AH2">
-        <v>1.099930001420454</v>
+        <v>1.099930001420448</v>
       </c>
       <c r="AI2">
-        <v>1.099886036097042</v>
+        <v>1.099886036097066</v>
       </c>
       <c r="AJ2">
-        <v>1.100030889719276</v>
+        <v>1.100030889719258</v>
       </c>
       <c r="AK2">
-        <v>1.099880693124304</v>
+        <v>1.099880693124298</v>
       </c>
       <c r="AL2">
-        <v>1.099778309979534</v>
+        <v>1.099778309979558</v>
       </c>
       <c r="AM2">
-        <v>-0.001322223408741087</v>
+        <v>-0.001322223407822956</v>
       </c>
       <c r="AN2">
-        <v>-120.0056648730202</v>
+        <v>-120.0056648730214</v>
       </c>
       <c r="AO2">
-        <v>119.9969120483124</v>
+        <v>119.9969120483128</v>
       </c>
       <c r="AP2">
-        <v>-0.003079220108437585</v>
+        <v>-0.00307922010751898</v>
       </c>
       <c r="AQ2">
-        <v>-120.0022649386088</v>
+        <v>-120.0022649386101</v>
       </c>
       <c r="AR2">
-        <v>119.9949506680922</v>
+        <v>119.9949506680926</v>
       </c>
     </row>
   </sheetData>
@@ -6163,130 +6163,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003600275133858633</v>
+        <v>0.0003600275132979262</v>
       </c>
       <c r="C2">
-        <v>0.7535960061791269</v>
+        <v>0.7535960061567664</v>
       </c>
       <c r="D2">
-        <v>0.6080598604022429</v>
+        <v>0.6080598604513535</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.7537826658973262</v>
+        <v>0.7537826658749115</v>
       </c>
       <c r="G2">
-        <v>0.6076998696776725</v>
+        <v>0.6076998697268716</v>
       </c>
       <c r="H2">
-        <v>0.004157239635379996</v>
+        <v>0.004157239634364584</v>
       </c>
       <c r="I2">
-        <v>8.701777140554917</v>
+        <v>8.70177714029672</v>
       </c>
       <c r="J2">
-        <v>7.021270481732824</v>
+        <v>7.021270482299905</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>8.703932501325902</v>
+        <v>8.703932501067078</v>
       </c>
       <c r="M2">
-        <v>7.017113666898094</v>
+        <v>7.017113667466197</v>
       </c>
       <c r="N2">
-        <v>0.00279780152186632</v>
+        <v>0.002797801521293709</v>
       </c>
       <c r="O2">
-        <v>2.064831237821028</v>
+        <v>2.064831237453104</v>
       </c>
       <c r="P2">
-        <v>0.9860335397347144</v>
+        <v>0.9860335399077896</v>
       </c>
       <c r="Q2">
-        <v>-4.283061085562759E-10</v>
+        <v>-4.283093218936924E-10</v>
       </c>
       <c r="R2">
-        <v>-0.7272810305623182</v>
+        <v>-0.7272810302591477</v>
       </c>
       <c r="S2">
-        <v>-0.4727028234421281</v>
+        <v>-0.4727028234184856</v>
       </c>
       <c r="T2">
-        <v>-0.002575099068705988</v>
+        <v>-0.002575099067875525</v>
       </c>
       <c r="U2">
-        <v>6.875450353375748</v>
+        <v>6.87545035315701</v>
       </c>
       <c r="V2">
-        <v>5.750708577708037</v>
+        <v>5.750708578287576</v>
       </c>
       <c r="W2">
-        <v>-1.200979931074386E-09</v>
+        <v>-1.200974863791773E-09</v>
       </c>
       <c r="X2">
-        <v>-7.236354773904477</v>
+        <v>-7.236354773784062</v>
       </c>
       <c r="Y2">
-        <v>-4.703334278581309</v>
+        <v>-4.703334279032443</v>
       </c>
       <c r="Z2">
-        <v>41.83518960472783</v>
+        <v>41.83518960295133</v>
       </c>
       <c r="AA2">
-        <v>163.0524781263406</v>
+        <v>163.0524781230077</v>
       </c>
       <c r="AB2">
-        <v>41.01575396609761</v>
+        <v>41.01575396650277</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-16.92411819985469</v>
+        <v>-16.92411820319231</v>
       </c>
       <c r="AE2">
-        <v>-138.9847314955676</v>
+        <v>-138.9847314951609</v>
       </c>
       <c r="AG2">
-        <v>0.9146638081463901</v>
+        <v>0.9146638081331698</v>
       </c>
       <c r="AH2">
-        <v>0.8249823172511271</v>
+        <v>0.8249823172393695</v>
       </c>
       <c r="AI2">
-        <v>0.8309935306255294</v>
+        <v>0.8309935306439321</v>
       </c>
       <c r="AJ2">
-        <v>0.9830927315586746</v>
+        <v>0.9830927315343865</v>
       </c>
       <c r="AK2">
-        <v>0.835577503896062</v>
+        <v>0.8355775039036606</v>
       </c>
       <c r="AL2">
-        <v>0.6736429002631675</v>
+        <v>0.6736429002722611</v>
       </c>
       <c r="AM2">
-        <v>-0.7913045708434845</v>
+        <v>-0.791304569255895</v>
       </c>
       <c r="AN2">
-        <v>-123.6635547352269</v>
+        <v>-123.6635547362496</v>
       </c>
       <c r="AO2">
-        <v>121.2862611148293</v>
+        <v>121.2862611145211</v>
       </c>
       <c r="AP2">
-        <v>-6.713373496042722</v>
+        <v>-6.713373495545341</v>
       </c>
       <c r="AQ2">
-        <v>-112.6632887658643</v>
+        <v>-112.6632887669203</v>
       </c>
       <c r="AR2">
-        <v>125.2760987186319</v>
+        <v>125.2760987198705</v>
       </c>
     </row>
   </sheetData>
@@ -6357,10 +6357,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006853945262934886</v>
+        <v>0.0006853945262934885</v>
       </c>
       <c r="C2">
-        <v>0.0006853945262934886</v>
+        <v>0.0006853945262934885</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6369,28 +6369,28 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0237427628553985</v>
+        <v>0.02374276285539849</v>
       </c>
       <c r="G2">
-        <v>0.0237427628553985</v>
+        <v>0.02374276285539849</v>
       </c>
       <c r="H2">
-        <v>0.01761866179579698</v>
+        <v>0.01761866179579696</v>
       </c>
       <c r="I2">
-        <v>-0.01761792896135745</v>
+        <v>-0.01761792896135743</v>
       </c>
       <c r="J2">
         <v>0.01763413071068529</v>
       </c>
       <c r="K2">
-        <v>-0.01763329922546793</v>
+        <v>-0.01763329922546794</v>
       </c>
       <c r="L2">
-        <v>-45.03017918754896</v>
+        <v>-45.030179187549</v>
       </c>
       <c r="M2">
-        <v>134.9698208124438</v>
+        <v>134.9698208124437</v>
       </c>
       <c r="N2">
         <v>1.049898497017663</v>
@@ -6399,10 +6399,10 @@
         <v>1.049851907180983</v>
       </c>
       <c r="P2">
-        <v>-0.005037818120266383</v>
+        <v>-0.005037818120266377</v>
       </c>
       <c r="Q2">
-        <v>-0.005197044997986881</v>
+        <v>-0.005197044997986874</v>
       </c>
     </row>
   </sheetData>
@@ -6554,130 +6554,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003410786921359991</v>
+        <v>0.0003410786920528471</v>
       </c>
       <c r="C2">
-        <v>0.7139330485314006</v>
+        <v>0.7139330485102163</v>
       </c>
       <c r="D2">
-        <v>0.5760567018230245</v>
+        <v>0.5760567018695498</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.7141098840514399</v>
+        <v>0.7141098840302043</v>
       </c>
       <c r="G2">
-        <v>0.5757156579834497</v>
+        <v>0.5757156580300586</v>
       </c>
       <c r="H2">
-        <v>0.003938437494391291</v>
+        <v>0.003938437493431135</v>
       </c>
       <c r="I2">
-        <v>8.243788755059485</v>
+        <v>8.243788754814871</v>
       </c>
       <c r="J2">
-        <v>6.651729837320223</v>
+        <v>6.651729837857452</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>8.245830675761425</v>
+        <v>8.245830675516217</v>
       </c>
       <c r="M2">
-        <v>6.647791802268545</v>
+        <v>6.647791802806738</v>
       </c>
       <c r="N2">
-        <v>0.002511046171209034</v>
+        <v>0.002511046170694927</v>
       </c>
       <c r="O2">
-        <v>1.853200283653016</v>
+        <v>1.853200283322568</v>
       </c>
       <c r="P2">
-        <v>0.8849719057212063</v>
+        <v>0.8849719058767279</v>
       </c>
       <c r="Q2">
-        <v>-3.844060774388987E-10</v>
+        <v>-3.844081552122291E-10</v>
       </c>
       <c r="R2">
-        <v>-0.6527397433003527</v>
+        <v>-0.6527397430280247</v>
       </c>
       <c r="S2">
-        <v>-0.4242540457739678</v>
+        <v>-0.4242540457529313</v>
       </c>
       <c r="T2">
-        <v>-0.002311169182808723</v>
+        <v>-0.002311169182066166</v>
       </c>
       <c r="U2">
-        <v>6.170764134003814</v>
+        <v>6.170764133807444</v>
       </c>
       <c r="V2">
-        <v>5.161300629421112</v>
+        <v>5.161300629940771</v>
       </c>
       <c r="W2">
-        <v>-1.077891195101043E-09</v>
+        <v>-1.077887618834271E-09</v>
       </c>
       <c r="X2">
-        <v>-6.494678341734026</v>
+        <v>-6.4946783416259</v>
       </c>
       <c r="Y2">
-        <v>-4.221274968883069</v>
+        <v>-4.221274969287486</v>
       </c>
       <c r="Z2">
-        <v>41.83518960470358</v>
+        <v>41.83518960296433</v>
       </c>
       <c r="AA2">
-        <v>163.0524781263407</v>
+        <v>163.0524781230076</v>
       </c>
       <c r="AB2">
-        <v>41.01575396609761</v>
+        <v>41.01575396650277</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-16.92411819985467</v>
+        <v>-16.92411820319235</v>
       </c>
       <c r="AE2">
-        <v>-138.9847314955676</v>
+        <v>-138.984731495161</v>
       </c>
       <c r="AG2">
-        <v>0.866523595635988</v>
+        <v>0.8665235956235099</v>
       </c>
       <c r="AH2">
-        <v>0.7815621843935403</v>
+        <v>0.781562184382388</v>
       </c>
       <c r="AI2">
-        <v>0.7872570180373097</v>
+        <v>0.7872570180546781</v>
       </c>
       <c r="AJ2">
-        <v>0.9313509958595538</v>
+        <v>0.931350995836589</v>
       </c>
       <c r="AK2">
-        <v>0.7915997294961556</v>
+        <v>0.7915997295033459</v>
       </c>
       <c r="AL2">
-        <v>0.638188001877696</v>
+        <v>0.6381880018862427</v>
       </c>
       <c r="AM2">
-        <v>-0.7913045708441681</v>
+        <v>-0.7913045692558944</v>
       </c>
       <c r="AN2">
-        <v>-123.6635547352286</v>
+        <v>-123.6635547362496</v>
       </c>
       <c r="AO2">
-        <v>121.2862611148322</v>
+        <v>121.2862611145211</v>
       </c>
       <c r="AP2">
-        <v>-6.713373496043643</v>
+        <v>-6.713373495545341</v>
       </c>
       <c r="AQ2">
-        <v>-112.6632887658662</v>
+        <v>-112.6632887669203</v>
       </c>
       <c r="AR2">
-        <v>125.2760987186351</v>
+        <v>125.2760987198705</v>
       </c>
     </row>
   </sheetData>
@@ -6832,127 +6832,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0006198989157093194</v>
+        <v>0.000619898915709399</v>
       </c>
       <c r="D2">
-        <v>0.0006203427371854434</v>
+        <v>0.0006203427371853921</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0006201176475451932</v>
+        <v>0.0006201176475451808</v>
       </c>
       <c r="G2">
-        <v>0.0006200167066454636</v>
+        <v>0.0006200167066455046</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.007157976117102654</v>
+        <v>0.007157976117103572</v>
       </c>
       <c r="J2">
-        <v>0.0071631009260769</v>
+        <v>0.007163100926076308</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007160501814789096</v>
+        <v>0.007160501814788952</v>
       </c>
       <c r="M2">
-        <v>0.007159336249676474</v>
+        <v>0.007159336249676946</v>
       </c>
       <c r="N2">
-        <v>1.609282785963515E-06</v>
+        <v>1.609282785129703E-06</v>
       </c>
       <c r="O2">
-        <v>0.004804550122668271</v>
+        <v>0.004804550122669068</v>
       </c>
       <c r="P2">
-        <v>0.004808456859925618</v>
+        <v>0.00480845685992579</v>
       </c>
       <c r="Q2">
-        <v>-6.505244051328291E-13</v>
+        <v>-6.505161644500557E-13</v>
       </c>
       <c r="R2">
-        <v>-0.004807315784223672</v>
+        <v>-0.004807315784223342</v>
       </c>
       <c r="S2">
-        <v>-0.004805750869382667</v>
+        <v>-0.004805750869383142</v>
       </c>
       <c r="T2">
-        <v>-3.270879998064745E-06</v>
+        <v>-3.270879997241775E-06</v>
       </c>
       <c r="U2">
-        <v>0.004811568620607492</v>
+        <v>0.004811568620607875</v>
       </c>
       <c r="V2">
-        <v>0.004814143195632913</v>
+        <v>0.004814143195632156</v>
       </c>
       <c r="W2">
-        <v>-9.329959143420503E-13</v>
+        <v>-9.329937176561104E-13</v>
       </c>
       <c r="X2">
-        <v>-0.004811721084315998</v>
+        <v>-0.004811721084316076</v>
       </c>
       <c r="Y2">
-        <v>-0.00481015473825574</v>
+        <v>-0.00481015473825611</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-165.0477474219279</v>
+        <v>-165.0477474219267</v>
       </c>
       <c r="AB2">
-        <v>74.96292645283313</v>
+        <v>74.962926452839</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>14.97537254540267</v>
+        <v>14.97537254539899</v>
       </c>
       <c r="AE2">
-        <v>-105.0311288498386</v>
+        <v>-105.0311288498376</v>
       </c>
       <c r="AG2">
-        <v>0.9499740262105582</v>
+        <v>0.9499740262105429</v>
       </c>
       <c r="AH2">
-        <v>0.9499367519435151</v>
+        <v>0.9499367519435097</v>
       </c>
       <c r="AI2">
-        <v>0.9498968407929926</v>
+        <v>0.9498968407930134</v>
       </c>
       <c r="AJ2">
-        <v>0.9500622310200825</v>
+        <v>0.9500622310200671</v>
       </c>
       <c r="AK2">
-        <v>0.9498896987196292</v>
+        <v>0.9498896987196236</v>
       </c>
       <c r="AL2">
-        <v>0.9497350785543011</v>
+        <v>0.9497350785543218</v>
       </c>
       <c r="AM2">
-        <v>-0.001389850200230465</v>
+        <v>-0.001389850199312684</v>
       </c>
       <c r="AN2">
-        <v>-120.0059290698722</v>
+        <v>-120.0059290698735</v>
       </c>
       <c r="AO2">
-        <v>119.9967845574099</v>
+        <v>119.9967845574102</v>
       </c>
       <c r="AP2">
-        <v>-0.005384351514918757</v>
+        <v>-0.005384351514000341</v>
       </c>
       <c r="AQ2">
-        <v>-119.9983872926524</v>
+        <v>-119.9983872926536</v>
       </c>
       <c r="AR2">
-        <v>119.9951113289364</v>
+        <v>119.9951113289367</v>
       </c>
     </row>
   </sheetData>
@@ -7107,127 +7107,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0005872726487996643</v>
+        <v>0.0005872726487997393</v>
       </c>
       <c r="D2">
-        <v>0.0005876931112448671</v>
+        <v>0.0005876931112448181</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.000587479868430761</v>
+        <v>0.0005874798684307489</v>
       </c>
       <c r="G2">
-        <v>0.0005873842402112979</v>
+        <v>0.0005873842402113362</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.006781240437443816</v>
+        <v>0.006781240437444681</v>
       </c>
       <c r="J2">
-        <v>0.006786095519562253</v>
+        <v>0.006786095519561689</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.006783633203639716</v>
+        <v>0.006783633203639576</v>
       </c>
       <c r="M2">
-        <v>0.006782528984074734</v>
+        <v>0.006782528984075176</v>
       </c>
       <c r="N2">
-        <v>1.444342404744678E-06</v>
+        <v>1.444342403995861E-06</v>
       </c>
       <c r="O2">
-        <v>0.00431211688735824</v>
+        <v>0.004312116887358955</v>
       </c>
       <c r="P2">
-        <v>0.004315623211003904</v>
+        <v>0.004315623211004056</v>
       </c>
       <c r="Q2">
-        <v>-5.838494657252016E-13</v>
+        <v>-5.83842179213808E-13</v>
       </c>
       <c r="R2">
-        <v>-0.004314599087687778</v>
+        <v>-0.004314599087687481</v>
       </c>
       <c r="S2">
-        <v>-0.004313194565819783</v>
+        <v>-0.004313194565820204</v>
       </c>
       <c r="T2">
-        <v>-2.935637367925266E-06</v>
+        <v>-2.935637367186205E-06</v>
       </c>
       <c r="U2">
-        <v>0.004318416037687597</v>
+        <v>0.004318416037687937</v>
       </c>
       <c r="V2">
-        <v>0.004320726736537947</v>
+        <v>0.004320726736537267</v>
       </c>
       <c r="W2">
-        <v>-8.373707757607213E-13</v>
+        <v>-8.37368694640951E-13</v>
       </c>
       <c r="X2">
-        <v>-0.004318552874918009</v>
+        <v>-0.004318552874918075</v>
       </c>
       <c r="Y2">
-        <v>-0.004317147068520857</v>
+        <v>-0.004317147068521186</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-165.0477474219279</v>
+        <v>-165.0477474219267</v>
       </c>
       <c r="AB2">
-        <v>74.96292645283312</v>
+        <v>74.96292645283897</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>14.97537254540264</v>
+        <v>14.97537254539899</v>
       </c>
       <c r="AE2">
-        <v>-105.0311288498386</v>
+        <v>-105.0311288498376</v>
       </c>
       <c r="AG2">
-        <v>0.8999753807041044</v>
+        <v>0.89997538070409</v>
       </c>
       <c r="AH2">
-        <v>0.8999400682410824</v>
+        <v>0.8999400682410772</v>
       </c>
       <c r="AI2">
-        <v>0.8999022576779565</v>
+        <v>0.8999022576779763</v>
       </c>
       <c r="AJ2">
-        <v>0.9000589431540675</v>
+        <v>0.9000589431540531</v>
       </c>
       <c r="AK2">
-        <v>0.8998954915032855</v>
+        <v>0.8998954915032802</v>
       </c>
       <c r="AL2">
-        <v>0.899749009243438</v>
+        <v>0.8997490092434577</v>
       </c>
       <c r="AM2">
-        <v>-0.001389850200231838</v>
+        <v>-0.001389850199312685</v>
       </c>
       <c r="AN2">
-        <v>-120.0059290698722</v>
+        <v>-120.0059290698735</v>
       </c>
       <c r="AO2">
-        <v>119.9967845574098</v>
+        <v>119.9967845574102</v>
       </c>
       <c r="AP2">
-        <v>-0.005384351514920131</v>
+        <v>-0.005384351514000342</v>
       </c>
       <c r="AQ2">
-        <v>-119.9983872926524</v>
+        <v>-119.9983872926536</v>
       </c>
       <c r="AR2">
-        <v>119.9951113289364</v>
+        <v>119.9951113289367</v>
       </c>
     </row>
   </sheetData>
@@ -7298,10 +7298,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0007180141641402969</v>
+        <v>0.0007180141641402973</v>
       </c>
       <c r="C2">
-        <v>0.0007180141641402969</v>
+        <v>0.0007180141641402973</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7310,10 +7310,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02487274025690187</v>
+        <v>0.02487274025690188</v>
       </c>
       <c r="G2">
-        <v>0.02487274025690187</v>
+        <v>0.02487274025690188</v>
       </c>
       <c r="H2">
         <v>0.01933569088618537</v>
@@ -7322,13 +7322,13 @@
         <v>-0.01933488663699852</v>
       </c>
       <c r="J2">
-        <v>0.01935347048976182</v>
+        <v>0.01935347048976184</v>
       </c>
       <c r="K2">
-        <v>-0.01935255797627465</v>
+        <v>-0.01935255797627467</v>
       </c>
       <c r="L2">
-        <v>-45.03136784807035</v>
+        <v>-45.03136784807037</v>
       </c>
       <c r="M2">
         <v>134.9686321519223</v>
@@ -7340,10 +7340,10 @@
         <v>1.099844930798715</v>
       </c>
       <c r="P2">
-        <v>-0.005037575241080466</v>
+        <v>-0.005037575241080462</v>
       </c>
       <c r="Q2">
-        <v>-0.005196745313343396</v>
+        <v>-0.00519674531334339</v>
       </c>
     </row>
   </sheetData>
@@ -7414,10 +7414,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.6889105335368642</v>
+        <v>0.6889105335368643</v>
       </c>
       <c r="C2">
-        <v>0.6889105335368642</v>
+        <v>0.6889105335368643</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7432,10 +7432,10 @@
         <v>23.86456091910463</v>
       </c>
       <c r="H2">
-        <v>3.243970258585425</v>
+        <v>3.243970258585431</v>
       </c>
       <c r="I2">
-        <v>-1.822455128673487</v>
+        <v>-1.822455128673493</v>
       </c>
       <c r="J2">
         <v>18.97323843541325</v>
@@ -7444,22 +7444,22 @@
         <v>-18.13320046022537</v>
       </c>
       <c r="L2">
-        <v>-81.35388246757608</v>
+        <v>-81.35388246757607</v>
       </c>
       <c r="M2">
-        <v>98.64611753241661</v>
+        <v>98.64611753241664</v>
       </c>
       <c r="N2">
-        <v>0.80657513724449</v>
+        <v>0.8065751372444899</v>
       </c>
       <c r="O2">
-        <v>0.7636659323883898</v>
+        <v>0.7636659323883896</v>
       </c>
       <c r="P2">
-        <v>-1.056274381063369</v>
+        <v>-1.056274381063373</v>
       </c>
       <c r="Q2">
-        <v>2.906947332764131</v>
+        <v>2.906947332764127</v>
       </c>
     </row>
   </sheetData>
@@ -7530,10 +7530,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.6526520753036733</v>
+        <v>0.6526520753036736</v>
       </c>
       <c r="C2">
-        <v>0.6526520753036733</v>
+        <v>0.6526520753036736</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7542,40 +7542,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22.60853108182462</v>
+        <v>22.60853108182463</v>
       </c>
       <c r="G2">
-        <v>22.60853108182462</v>
+        <v>22.60853108182463</v>
       </c>
       <c r="H2">
-        <v>2.911485691061011</v>
+        <v>2.911485691061017</v>
       </c>
       <c r="I2">
-        <v>-1.635666053253948</v>
+        <v>-1.635666053253954</v>
       </c>
       <c r="J2">
-        <v>17.02861241455484</v>
+        <v>17.02861241455485</v>
       </c>
       <c r="K2">
         <v>-16.27467253541</v>
       </c>
       <c r="L2">
-        <v>-81.35388246757608</v>
+        <v>-81.35388246757607</v>
       </c>
       <c r="M2">
-        <v>98.64611753241662</v>
+        <v>98.64611753241664</v>
       </c>
       <c r="N2">
         <v>0.764123803577744</v>
       </c>
       <c r="O2">
-        <v>0.7234729784913748</v>
+        <v>0.7234729784913747</v>
       </c>
       <c r="P2">
-        <v>-1.05627438106337</v>
+        <v>-1.056274381063373</v>
       </c>
       <c r="Q2">
-        <v>2.90694733276413</v>
+        <v>2.906947332764127</v>
       </c>
     </row>
   </sheetData>
@@ -7646,10 +7646,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.00062008748781697</v>
+        <v>0.0006200874878169702</v>
       </c>
       <c r="C2">
-        <v>0.00062008748781697</v>
+        <v>0.0006200874878169702</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7658,25 +7658,25 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02148046068073478</v>
+        <v>0.02148046068073479</v>
       </c>
       <c r="G2">
-        <v>0.02148046068073478</v>
+        <v>0.02148046068073479</v>
       </c>
       <c r="H2">
-        <v>0.01442169622637078</v>
+        <v>0.01442169622637079</v>
       </c>
       <c r="I2">
-        <v>-0.01442054454651014</v>
+        <v>-0.01442054454651015</v>
       </c>
       <c r="J2">
         <v>0.01443443974596179</v>
       </c>
       <c r="K2">
-        <v>-0.01443375916592586</v>
+        <v>-0.01443375916592585</v>
       </c>
       <c r="L2">
-        <v>-45.03057032873991</v>
+        <v>-45.03057032873988</v>
       </c>
       <c r="M2">
         <v>134.9694296712528</v>
@@ -7688,10 +7688,10 @@
         <v>0.9498435003064266</v>
       </c>
       <c r="P2">
-        <v>-0.005267223643389584</v>
+        <v>-0.005267223643389585</v>
       </c>
       <c r="Q2">
-        <v>-0.004330157604604892</v>
+        <v>-0.004330157604604893</v>
       </c>
     </row>
   </sheetData>
@@ -7762,10 +7762,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0005874512960570529</v>
+        <v>0.0005874512960570532</v>
       </c>
       <c r="C2">
-        <v>0.0005874512960570529</v>
+        <v>0.0005874512960570532</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7774,16 +7774,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02034990983486004</v>
+        <v>0.02034990983486005</v>
       </c>
       <c r="G2">
-        <v>0.02034990983486004</v>
+        <v>0.02034990983486005</v>
       </c>
       <c r="H2">
-        <v>0.01294357187547605</v>
+        <v>0.01294357187547606</v>
       </c>
       <c r="I2">
-        <v>-0.01294253823485433</v>
+        <v>-0.01294253823485434</v>
       </c>
       <c r="J2">
         <v>0.01295500927224158</v>
@@ -7792,7 +7792,7 @@
         <v>-0.0129543984469632</v>
       </c>
       <c r="L2">
-        <v>-45.03057032873992</v>
+        <v>-45.0305703287399</v>
       </c>
       <c r="M2">
         <v>134.9694296712528</v>
@@ -7804,10 +7804,10 @@
         <v>0.8998517245861249</v>
       </c>
       <c r="P2">
-        <v>-0.005267223643389584</v>
+        <v>-0.005267223643389587</v>
       </c>
       <c r="Q2">
-        <v>-0.004330157604604892</v>
+        <v>-0.004330157604604894</v>
       </c>
     </row>
   </sheetData>
@@ -7959,127 +7959,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6936925140491841</v>
+        <v>0.6936925140491743</v>
       </c>
       <c r="D2">
-        <v>0.6936925140491839</v>
+        <v>0.6936925140491765</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.6936925140491838</v>
+        <v>0.6936925140491743</v>
       </c>
       <c r="G2">
-        <v>0.6936925140491838</v>
+        <v>0.6936925140491768</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>8.010071194422494</v>
+        <v>8.010071194422382</v>
       </c>
       <c r="J2">
-        <v>8.010071194422492</v>
+        <v>8.010071194422407</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>8.01007119442249</v>
+        <v>8.010071194422382</v>
       </c>
       <c r="M2">
-        <v>8.01007119442249</v>
+        <v>8.010071194422411</v>
       </c>
       <c r="N2">
-        <v>-1.243449731109628E-15</v>
+        <v>2.238209515997369E-14</v>
       </c>
       <c r="O2">
-        <v>5.010515246466213</v>
+        <v>5.010515246465553</v>
       </c>
       <c r="P2">
-        <v>-3.337253959230821</v>
+        <v>-3.337253959231214</v>
       </c>
       <c r="Q2">
-        <v>-4.637993038794352E-29</v>
+        <v>-2.362554489108333E-14</v>
       </c>
       <c r="R2">
-        <v>-4.760286403198496</v>
+        <v>-4.760286403197854</v>
       </c>
       <c r="S2">
-        <v>3.587482802498534</v>
+        <v>3.587482802498929</v>
       </c>
       <c r="T2">
-        <v>1.865174596664542E-15</v>
+        <v>-2.48689946221926E-15</v>
       </c>
       <c r="U2">
-        <v>5.605578333214116</v>
+        <v>5.605578333214094</v>
       </c>
       <c r="V2">
-        <v>6.631497705500343</v>
+        <v>6.631497705499552</v>
       </c>
       <c r="W2">
-        <v>-1.865174596664511E-15</v>
+        <v>3.108624327774086E-15</v>
       </c>
       <c r="X2">
-        <v>-5.321664842104929</v>
+        <v>-5.321664842104915</v>
       </c>
       <c r="Y2">
-        <v>-6.347584214391158</v>
+        <v>-6.347584214390373</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-172.9936292747861</v>
+        <v>-172.9936292747915</v>
       </c>
       <c r="AB2">
-        <v>7.006370725206573</v>
+        <v>7.006370725201169</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>7.006370725206584</v>
+        <v>7.006370725201217</v>
       </c>
       <c r="AE2">
-        <v>-172.9936292747861</v>
+        <v>-172.9936292747915</v>
       </c>
       <c r="AF2">
-        <v>1.049999952314901</v>
+        <v>1.04999995231488</v>
       </c>
       <c r="AG2">
-        <v>0.9386302707479933</v>
+        <v>0.9386302707479496</v>
       </c>
       <c r="AH2">
-        <v>0.9268184944732195</v>
+        <v>0.9268184944731632</v>
       </c>
       <c r="AI2">
-        <v>1.049999952314901</v>
+        <v>1.04999995231488</v>
       </c>
       <c r="AJ2">
-        <v>0.8913852178495338</v>
+        <v>0.8913852178494909</v>
       </c>
       <c r="AK2">
-        <v>0.9102563143323492</v>
+        <v>0.9102563143322974</v>
       </c>
       <c r="AL2">
-        <v>-1.424859017936183E-12</v>
+        <v>9.790990300149927E-14</v>
       </c>
       <c r="AM2">
-        <v>-124.7853905097038</v>
+        <v>-124.7853905097055</v>
       </c>
       <c r="AN2">
         <v>123.719871368878</v>
       </c>
       <c r="AO2">
-        <v>-1.424732177937545E-12</v>
+        <v>8.642620113146718E-14</v>
       </c>
       <c r="AP2">
-        <v>-124.8066037900598</v>
+        <v>-124.8066037900614</v>
       </c>
       <c r="AQ2">
-        <v>126.4803292649316</v>
+        <v>126.4803292649319</v>
       </c>
     </row>
   </sheetData>
